--- a/docs/缺牌價清單.xlsx
+++ b/docs/缺牌價清單.xlsx
@@ -10,7 +10,7 @@
     <sheet name="缺牌價清單" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'缺牌價清單'!$A$1:$H$599</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'缺牌價清單'!$A$1:$H$561</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +30,6 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -449,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H599"/>
+  <dimension ref="A1:H561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12135,7 +12134,7 @@
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-252</t>
+          <t>PL-RT-266</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
@@ -12145,7 +12144,7 @@
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>PVC W 1.2 m/m</t>
+          <t>PVC W 150 m/m2</t>
         </is>
       </c>
       <c r="D325" s="2" t="inlineStr">
@@ -12164,14 +12163,14 @@
         </is>
       </c>
       <c r="G325" s="2" t="n">
-        <v>0.002</v>
+        <v>0.038</v>
       </c>
       <c r="H325" s="3" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-253</t>
+          <t>PL-RT-267</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
@@ -12181,7 +12180,7 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>PVC W 1.6 m/m</t>
+          <t>PVC W 200 m/m2</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
@@ -12200,14 +12199,14 @@
         </is>
       </c>
       <c r="G326" s="2" t="n">
-        <v>0.002</v>
+        <v>0.043</v>
       </c>
       <c r="H326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-264</t>
+          <t>PL-RT-268</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
@@ -12217,7 +12216,7 @@
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>PVC W 100 m/m2</t>
+          <t>PVC W 250 m/m2</t>
         </is>
       </c>
       <c r="D327" s="2" t="inlineStr">
@@ -12236,14 +12235,14 @@
         </is>
       </c>
       <c r="G327" s="2" t="n">
-        <v>0.028</v>
+        <v>0.051</v>
       </c>
       <c r="H327" s="3" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-265</t>
+          <t>PL-RT-269</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
@@ -12253,7 +12252,7 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>PVC W 125 m/m2</t>
+          <t>PVC W 325 m/m2</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
@@ -12272,24 +12271,24 @@
         </is>
       </c>
       <c r="G328" s="2" t="n">
-        <v>0.03</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H328" s="3" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-257</t>
+          <t>PL-RT-311</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>PVC W 14 m/m2</t>
+          <t>２Ｃ PVC 1.6 m/m2 白扁線</t>
         </is>
       </c>
       <c r="D329" s="2" t="inlineStr">
@@ -12308,24 +12307,24 @@
         </is>
       </c>
       <c r="G329" s="2" t="n">
-        <v>0.007</v>
+        <v>0.005</v>
       </c>
       <c r="H329" s="3" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-266</t>
+          <t>PL-RT-312</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>PVC W 150 m/m2</t>
+          <t>２Ｃ PVC 2.0 m/m2 白扁線</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
@@ -12344,24 +12343,24 @@
         </is>
       </c>
       <c r="G330" s="2" t="n">
-        <v>0.038</v>
+        <v>0.006</v>
       </c>
       <c r="H330" s="3" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-254</t>
+          <t>PL-RT-295</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>PVC W 2.0 m/m</t>
+          <t>２Ｃ PVC 電纜 1.25 m/m2</t>
         </is>
       </c>
       <c r="D331" s="2" t="inlineStr">
@@ -12380,24 +12379,24 @@
         </is>
       </c>
       <c r="G331" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H331" s="3" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-267</t>
+          <t>PL-RT-296</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>PVC W 200 m/m2</t>
+          <t>２Ｃ PVC 電纜 1.6 m/m2</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
@@ -12416,24 +12415,24 @@
         </is>
       </c>
       <c r="G332" s="2" t="n">
-        <v>0.043</v>
+        <v>0.005</v>
       </c>
       <c r="H332" s="3" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-258</t>
+          <t>PL-RT-308</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>PVC W 22 m/m2</t>
+          <t>２Ｃ PVC 電纜 100 m/m2</t>
         </is>
       </c>
       <c r="D333" s="2" t="inlineStr">
@@ -12452,24 +12451,24 @@
         </is>
       </c>
       <c r="G333" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.045</v>
       </c>
       <c r="H333" s="3" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-268</t>
+          <t>PL-RT-309</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>PVC W 250 m/m2</t>
+          <t>２Ｃ PVC 電纜 125 m/m2</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
@@ -12488,24 +12487,24 @@
         </is>
       </c>
       <c r="G334" s="2" t="n">
-        <v>0.051</v>
+        <v>0.052</v>
       </c>
       <c r="H334" s="3" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-259</t>
+          <t>PL-RT-310</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>PVC W 30 m/m2</t>
+          <t>２Ｃ PVC 電纜 150 m/m2</t>
         </is>
       </c>
       <c r="D335" s="2" t="inlineStr">
@@ -12524,24 +12523,24 @@
         </is>
       </c>
       <c r="G335" s="2" t="n">
-        <v>0.011</v>
+        <v>0.065</v>
       </c>
       <c r="H335" s="3" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-269</t>
+          <t>PL-RT-305</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>PVC W 325 m/m2</t>
+          <t>２Ｃ PVC 電纜 50 m/m2</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
@@ -12560,24 +12559,24 @@
         </is>
       </c>
       <c r="G336" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.028</v>
       </c>
       <c r="H336" s="3" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-260</t>
+          <t>PL-RT-306</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>PVC W 38 m/m2</t>
+          <t>２Ｃ PVC 電纜 60 m/m2</t>
         </is>
       </c>
       <c r="D337" s="2" t="inlineStr">
@@ -12596,24 +12595,24 @@
         </is>
       </c>
       <c r="G337" s="2" t="n">
-        <v>0.013</v>
+        <v>0.032</v>
       </c>
       <c r="H337" s="3" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-255</t>
+          <t>PL-RT-307</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>PVC W 5.5 m/m2</t>
+          <t>２Ｃ PVC 電纜 80 m/m2</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
@@ -12632,24 +12631,24 @@
         </is>
       </c>
       <c r="G338" s="2" t="n">
-        <v>0.005</v>
+        <v>0.038</v>
       </c>
       <c r="H338" s="3" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-261</t>
+          <t>PL-RT-313</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>PVC W 50 m/m2</t>
+          <t>３Ｃ PVC 電纜 1.25 m/m2</t>
         </is>
       </c>
       <c r="D339" s="2" t="inlineStr">
@@ -12668,24 +12667,24 @@
         </is>
       </c>
       <c r="G339" s="2" t="n">
-        <v>0.014</v>
+        <v>0.005</v>
       </c>
       <c r="H339" s="3" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-262</t>
+          <t>PL-RT-314</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>PVC W 60 m/m2</t>
+          <t>３Ｃ PVC 電纜 1.6 m/m2</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
@@ -12704,24 +12703,24 @@
         </is>
       </c>
       <c r="G340" s="2" t="n">
-        <v>0.018</v>
+        <v>0.006</v>
       </c>
       <c r="H340" s="3" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-256</t>
+          <t>PL-RT-326</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>PVC W 8.0 m/m2</t>
+          <t>３Ｃ PVC 電纜 100 m/m2</t>
         </is>
       </c>
       <c r="D341" s="2" t="inlineStr">
@@ -12740,24 +12739,24 @@
         </is>
       </c>
       <c r="G341" s="2" t="n">
-        <v>0.006</v>
+        <v>0.052</v>
       </c>
       <c r="H341" s="3" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-263</t>
+          <t>PL-RT-327</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>PVC電線</t>
+          <t>PVC電纜線</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>PVC W 80 m/m2</t>
+          <t>３Ｃ PVC 電纜 125 m/m2</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
@@ -12776,14 +12775,14 @@
         </is>
       </c>
       <c r="G342" s="2" t="n">
-        <v>0.021</v>
+        <v>0.062</v>
       </c>
       <c r="H342" s="3" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-311</t>
+          <t>PL-RT-328</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
@@ -12793,7 +12792,7 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 1.6 m/m2 白扁線</t>
+          <t>３Ｃ PVC 電纜 150 m/m2</t>
         </is>
       </c>
       <c r="D343" s="2" t="inlineStr">
@@ -12812,14 +12811,14 @@
         </is>
       </c>
       <c r="G343" s="2" t="n">
-        <v>0.005</v>
+        <v>0.075</v>
       </c>
       <c r="H343" s="3" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-312</t>
+          <t>PL-RT-323</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
@@ -12829,7 +12828,7 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 2.0 m/m2 白扁線</t>
+          <t>３Ｃ PVC 電纜 50 m/m2</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
@@ -12848,14 +12847,14 @@
         </is>
       </c>
       <c r="G344" s="2" t="n">
-        <v>0.006</v>
+        <v>0.032</v>
       </c>
       <c r="H344" s="3" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-295</t>
+          <t>PL-RT-324</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
@@ -12865,7 +12864,7 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 1.25 m/m2</t>
+          <t>３Ｃ PVC 電纜 60 m/m2</t>
         </is>
       </c>
       <c r="D345" s="2" t="inlineStr">
@@ -12884,14 +12883,14 @@
         </is>
       </c>
       <c r="G345" s="2" t="n">
-        <v>0.004</v>
+        <v>0.042</v>
       </c>
       <c r="H345" s="3" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-296</t>
+          <t>PL-RT-325</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
@@ -12901,7 +12900,7 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 1.6 m/m2</t>
+          <t>３Ｃ PVC 電纜 80 m/m2</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
@@ -12920,14 +12919,14 @@
         </is>
       </c>
       <c r="G346" s="2" t="n">
-        <v>0.005</v>
+        <v>0.044</v>
       </c>
       <c r="H346" s="3" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-308</t>
+          <t>PL-RT-329</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
@@ -12937,7 +12936,7 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 100 m/m2</t>
+          <t>４Ｃ PVC 電纜 1.25 m/m2</t>
         </is>
       </c>
       <c r="D347" s="2" t="inlineStr">
@@ -12956,14 +12955,14 @@
         </is>
       </c>
       <c r="G347" s="2" t="n">
-        <v>0.045</v>
+        <v>0.007</v>
       </c>
       <c r="H347" s="3" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-309</t>
+          <t>PL-RT-330</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -12973,7 +12972,7 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 125 m/m2</t>
+          <t>４Ｃ PVC 電纜 1.6 m/m2</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
@@ -12992,14 +12991,14 @@
         </is>
       </c>
       <c r="G348" s="2" t="n">
-        <v>0.052</v>
+        <v>0.008</v>
       </c>
       <c r="H348" s="3" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-301</t>
+          <t>PL-RT-342</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
@@ -13009,7 +13008,7 @@
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 14 m/m2</t>
+          <t>４Ｃ PVC 電纜 100 m/m2</t>
         </is>
       </c>
       <c r="D349" s="2" t="inlineStr">
@@ -13028,14 +13027,14 @@
         </is>
       </c>
       <c r="G349" s="2" t="n">
-        <v>0.012</v>
+        <v>0.068</v>
       </c>
       <c r="H349" s="3" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-310</t>
+          <t>PL-RT-343</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
@@ -13045,7 +13044,7 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 150 m/m2</t>
+          <t>４Ｃ PVC 電纜 125 m/m2</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
@@ -13064,14 +13063,14 @@
         </is>
       </c>
       <c r="G350" s="2" t="n">
-        <v>0.065</v>
+        <v>0.08</v>
       </c>
       <c r="H350" s="3" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-297</t>
+          <t>PL-RT-344</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
@@ -13081,7 +13080,7 @@
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 2.0 m/m2</t>
+          <t>４Ｃ PVC 電纜 150 m/m2</t>
         </is>
       </c>
       <c r="D351" s="2" t="inlineStr">
@@ -13100,14 +13099,14 @@
         </is>
       </c>
       <c r="G351" s="2" t="n">
-        <v>0.006</v>
+        <v>0.092</v>
       </c>
       <c r="H351" s="3" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-302</t>
+          <t>PL-RT-339</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
@@ -13117,7 +13116,7 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 22 m/m2</t>
+          <t>４Ｃ PVC 電纜 50 m/m2</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
@@ -13136,14 +13135,14 @@
         </is>
       </c>
       <c r="G352" s="2" t="n">
-        <v>0.016</v>
+        <v>0.048</v>
       </c>
       <c r="H352" s="3" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-298</t>
+          <t>PL-RT-340</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
@@ -13153,7 +13152,7 @@
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 3.5 m/m2</t>
+          <t>４Ｃ PVC 電纜 60 m/m2</t>
         </is>
       </c>
       <c r="D353" s="2" t="inlineStr">
@@ -13172,14 +13171,14 @@
         </is>
       </c>
       <c r="G353" s="2" t="n">
-        <v>0.007</v>
+        <v>0.056</v>
       </c>
       <c r="H353" s="3" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-303</t>
+          <t>PL-RT-341</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
@@ -13189,7 +13188,7 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 30 m/m2</t>
+          <t>４Ｃ PVC 電纜 80 m/m2</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
@@ -13208,24 +13207,24 @@
         </is>
       </c>
       <c r="G354" s="2" t="n">
-        <v>0.018</v>
+        <v>0.062</v>
       </c>
       <c r="H354" s="3" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-304</t>
+          <t>PL-RT-356</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 38 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 100 m/m2</t>
         </is>
       </c>
       <c r="D355" s="2" t="inlineStr">
@@ -13244,24 +13243,24 @@
         </is>
       </c>
       <c r="G355" s="2" t="n">
-        <v>0.022</v>
+        <v>0.046</v>
       </c>
       <c r="H355" s="3" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-299</t>
+          <t>PL-RT-367</t>
         </is>
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 5.5 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 1000 m/m2</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
@@ -13280,24 +13279,24 @@
         </is>
       </c>
       <c r="G356" s="2" t="n">
-        <v>0.008</v>
+        <v>0.315</v>
       </c>
       <c r="H356" s="3" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-305</t>
+          <t>PL-RT-357</t>
         </is>
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 50 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 125 m/m2</t>
         </is>
       </c>
       <c r="D357" s="2" t="inlineStr">
@@ -13316,24 +13315,24 @@
         </is>
       </c>
       <c r="G357" s="2" t="n">
-        <v>0.028</v>
+        <v>0.054</v>
       </c>
       <c r="H357" s="3" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-306</t>
+          <t>PL-RT-349</t>
         </is>
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 60 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 14 m/m2</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
@@ -13352,24 +13351,24 @@
         </is>
       </c>
       <c r="G358" s="2" t="n">
-        <v>0.032</v>
+        <v>0.012</v>
       </c>
       <c r="H358" s="3" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-300</t>
+          <t>PL-RT-358</t>
         </is>
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 8 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 150 m/m2</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
@@ -13388,24 +13387,24 @@
         </is>
       </c>
       <c r="G359" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.057</v>
       </c>
       <c r="H359" s="3" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-307</t>
+          <t>PL-RT-345</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>２Ｃ PVC 電纜 80 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 2.0 m/m2</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
@@ -13424,24 +13423,24 @@
         </is>
       </c>
       <c r="G360" s="2" t="n">
-        <v>0.038</v>
+        <v>0.004</v>
       </c>
       <c r="H360" s="3" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-313</t>
+          <t>PL-RT-359</t>
         </is>
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 1.25 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 200 m/m2</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
@@ -13460,24 +13459,24 @@
         </is>
       </c>
       <c r="G361" s="2" t="n">
-        <v>0.005</v>
+        <v>0.065</v>
       </c>
       <c r="H361" s="3" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-314</t>
+          <t>PL-RT-350</t>
         </is>
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 1.6 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 22 m/m2</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
@@ -13496,24 +13495,24 @@
         </is>
       </c>
       <c r="G362" s="2" t="n">
-        <v>0.006</v>
+        <v>0.015</v>
       </c>
       <c r="H362" s="3" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-326</t>
+          <t>PL-RT-360</t>
         </is>
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 100 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 250 m/m2</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
@@ -13532,24 +13531,24 @@
         </is>
       </c>
       <c r="G363" s="2" t="n">
-        <v>0.052</v>
+        <v>0.075</v>
       </c>
       <c r="H363" s="3" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-327</t>
+          <t>PL-RT-346</t>
         </is>
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 125 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 3.5 m/m2</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
@@ -13568,24 +13567,24 @@
         </is>
       </c>
       <c r="G364" s="2" t="n">
-        <v>0.062</v>
+        <v>0.005</v>
       </c>
       <c r="H364" s="3" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-319</t>
+          <t>PL-RT-351</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 14 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 30 m/m2</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
@@ -13604,24 +13603,24 @@
         </is>
       </c>
       <c r="G365" s="2" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="H365" s="3" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-328</t>
+          <t>PL-RT-361</t>
         </is>
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 150 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 325 m/m2</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
@@ -13640,24 +13639,24 @@
         </is>
       </c>
       <c r="G366" s="2" t="n">
-        <v>0.075</v>
+        <v>0.117</v>
       </c>
       <c r="H366" s="3" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-315</t>
+          <t>PL-RT-352</t>
         </is>
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 2.0 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 38 m/m2</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
@@ -13676,24 +13675,24 @@
         </is>
       </c>
       <c r="G367" s="2" t="n">
-        <v>0.007</v>
+        <v>0.021</v>
       </c>
       <c r="H367" s="3" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-320</t>
+          <t>PL-RT-362</t>
         </is>
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 22 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 400 m/m2</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
@@ -13712,24 +13711,24 @@
         </is>
       </c>
       <c r="G368" s="2" t="n">
-        <v>0.022</v>
+        <v>0.128</v>
       </c>
       <c r="H368" s="3" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-316</t>
+          <t>PL-RT-347</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 3.5 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 5.5 m/m2</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
@@ -13755,17 +13754,17 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-321</t>
+          <t>PL-RT-353</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 30 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 50 m/m2</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
@@ -13784,24 +13783,24 @@
         </is>
       </c>
       <c r="G370" s="2" t="n">
-        <v>0.024</v>
+        <v>0.023</v>
       </c>
       <c r="H370" s="3" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-322</t>
+          <t>PL-RT-363</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 38 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 500 m/m2</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
@@ -13820,24 +13819,24 @@
         </is>
       </c>
       <c r="G371" s="2" t="n">
-        <v>0.028</v>
+        <v>0.154</v>
       </c>
       <c r="H371" s="3" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-317</t>
+          <t>PL-RT-354</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 5.5 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 60 m/m2</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
@@ -13856,24 +13855,24 @@
         </is>
       </c>
       <c r="G372" s="2" t="n">
-        <v>0.01</v>
+        <v>0.029</v>
       </c>
       <c r="H372" s="3" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-323</t>
+          <t>PL-RT-364</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 50 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 600 m/m2</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
@@ -13892,24 +13891,24 @@
         </is>
       </c>
       <c r="G373" s="2" t="n">
-        <v>0.032</v>
+        <v>0.185</v>
       </c>
       <c r="H373" s="3" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-324</t>
+          <t>PL-RT-365</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 60 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 725 m/m2</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
@@ -13928,24 +13927,24 @@
         </is>
       </c>
       <c r="G374" s="2" t="n">
-        <v>0.042</v>
+        <v>0.22</v>
       </c>
       <c r="H374" s="3" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-318</t>
+          <t>PL-RT-348</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 8 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 8 m/m2</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
@@ -13964,24 +13963,24 @@
         </is>
       </c>
       <c r="G375" s="2" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="H375" s="3" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-325</t>
+          <t>PL-RT-355</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ PVC 電纜 80 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 80 m/m2</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
@@ -14000,24 +13999,24 @@
         </is>
       </c>
       <c r="G376" s="2" t="n">
-        <v>0.044</v>
+        <v>0.035</v>
       </c>
       <c r="H376" s="3" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-329</t>
+          <t>PL-RT-366</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 1.25 m/m2</t>
+          <t>１Ｃ XLPE 電力電纜 800 m/m2</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
@@ -14036,24 +14035,24 @@
         </is>
       </c>
       <c r="G377" s="2" t="n">
-        <v>0.007</v>
+        <v>0.26</v>
       </c>
       <c r="H377" s="3" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-330</t>
+          <t>PL-RT-379</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 1.6 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 100 m/m2</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
@@ -14072,24 +14071,24 @@
         </is>
       </c>
       <c r="G378" s="2" t="n">
-        <v>0.008</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H378" s="3" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-342</t>
+          <t>PL-RT-390</t>
         </is>
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 100 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 1000 m/m2</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
@@ -14108,24 +14107,24 @@
         </is>
       </c>
       <c r="G379" s="2" t="n">
-        <v>0.068</v>
+        <v>0.475</v>
       </c>
       <c r="H379" s="3" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-343</t>
+          <t>PL-RT-380</t>
         </is>
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 125 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 125 m/m2</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
@@ -14144,24 +14143,24 @@
         </is>
       </c>
       <c r="G380" s="2" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="H380" s="3" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-335</t>
+          <t>PL-RT-372</t>
         </is>
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 14 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 14 m/m2</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
@@ -14180,24 +14179,24 @@
         </is>
       </c>
       <c r="G381" s="2" t="n">
-        <v>0.024</v>
+        <v>0.017</v>
       </c>
       <c r="H381" s="3" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-344</t>
+          <t>PL-RT-381</t>
         </is>
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 150 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 150 m/m2</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
@@ -14216,24 +14215,24 @@
         </is>
       </c>
       <c r="G382" s="2" t="n">
-        <v>0.092</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H382" s="3" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-331</t>
+          <t>PL-RT-368</t>
         </is>
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 2.0 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 2.0 m/m2</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
@@ -14252,24 +14251,24 @@
         </is>
       </c>
       <c r="G383" s="2" t="n">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="H383" s="3" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-336</t>
+          <t>PL-RT-382</t>
         </is>
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 22 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 200 m/m2</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
@@ -14288,24 +14287,24 @@
         </is>
       </c>
       <c r="G384" s="2" t="n">
-        <v>0.03</v>
+        <v>0.095</v>
       </c>
       <c r="H384" s="3" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-332</t>
+          <t>PL-RT-373</t>
         </is>
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 3.5 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 22 m/m2</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
@@ -14324,24 +14323,24 @@
         </is>
       </c>
       <c r="G385" s="2" t="n">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="H385" s="3" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-337</t>
+          <t>PL-RT-383</t>
         </is>
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 30 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 250 m/m2</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
@@ -14360,24 +14359,24 @@
         </is>
       </c>
       <c r="G386" s="2" t="n">
-        <v>0.036</v>
+        <v>0.112</v>
       </c>
       <c r="H386" s="3" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-338</t>
+          <t>PL-RT-369</t>
         </is>
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 38 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 3.5 m/m2</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
@@ -14396,24 +14395,24 @@
         </is>
       </c>
       <c r="G387" s="2" t="n">
-        <v>0.04</v>
+        <v>0.008</v>
       </c>
       <c r="H387" s="3" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-333</t>
+          <t>PL-RT-374</t>
         </is>
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 5.5 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 30 m/m2</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
@@ -14432,24 +14431,24 @@
         </is>
       </c>
       <c r="G388" s="2" t="n">
-        <v>0.016</v>
+        <v>0.03</v>
       </c>
       <c r="H388" s="3" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-339</t>
+          <t>PL-RT-384</t>
         </is>
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 50 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 325 m/m2</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
@@ -14468,24 +14467,24 @@
         </is>
       </c>
       <c r="G389" s="2" t="n">
-        <v>0.048</v>
+        <v>0.16</v>
       </c>
       <c r="H389" s="3" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-340</t>
+          <t>PL-RT-375</t>
         </is>
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 60 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 38 m/m2</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
@@ -14504,24 +14503,24 @@
         </is>
       </c>
       <c r="G390" s="2" t="n">
-        <v>0.056</v>
+        <v>0.034</v>
       </c>
       <c r="H390" s="3" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-334</t>
+          <t>PL-RT-385</t>
         </is>
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 8 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 400 m/m2</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
@@ -14540,24 +14539,24 @@
         </is>
       </c>
       <c r="G391" s="2" t="n">
-        <v>0.018</v>
+        <v>0.211</v>
       </c>
       <c r="H391" s="3" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-341</t>
+          <t>PL-RT-370</t>
         </is>
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>PVC電纜線</t>
+          <t>XLPE電纜</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>４Ｃ PVC 電纜 80 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 5.5 m/m2</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
@@ -14576,14 +14575,14 @@
         </is>
       </c>
       <c r="G392" s="2" t="n">
-        <v>0.062</v>
+        <v>0.013</v>
       </c>
       <c r="H392" s="3" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-356</t>
+          <t>PL-RT-376</t>
         </is>
       </c>
       <c r="B393" s="2" t="inlineStr">
@@ -14593,7 +14592,7 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 100 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 50 m/m2</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
@@ -14612,14 +14611,14 @@
         </is>
       </c>
       <c r="G393" s="2" t="n">
-        <v>0.046</v>
+        <v>0.038</v>
       </c>
       <c r="H393" s="3" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-367</t>
+          <t>PL-RT-386</t>
         </is>
       </c>
       <c r="B394" s="2" t="inlineStr">
@@ -14629,7 +14628,7 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 1000 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 500 m/m2</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
@@ -14648,14 +14647,14 @@
         </is>
       </c>
       <c r="G394" s="2" t="n">
-        <v>0.315</v>
+        <v>0.254</v>
       </c>
       <c r="H394" s="3" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-357</t>
+          <t>PL-RT-377</t>
         </is>
       </c>
       <c r="B395" s="2" t="inlineStr">
@@ -14665,7 +14664,7 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 125 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 60 m/m2</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
@@ -14684,14 +14683,14 @@
         </is>
       </c>
       <c r="G395" s="2" t="n">
-        <v>0.054</v>
+        <v>0.045</v>
       </c>
       <c r="H395" s="3" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-349</t>
+          <t>PL-RT-387</t>
         </is>
       </c>
       <c r="B396" s="2" t="inlineStr">
@@ -14701,7 +14700,7 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 14 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 600 m/m2</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
@@ -14720,14 +14719,14 @@
         </is>
       </c>
       <c r="G396" s="2" t="n">
-        <v>0.012</v>
+        <v>0.285</v>
       </c>
       <c r="H396" s="3" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-358</t>
+          <t>PL-RT-388</t>
         </is>
       </c>
       <c r="B397" s="2" t="inlineStr">
@@ -14737,7 +14736,7 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 150 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 725 m/m2</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
@@ -14756,14 +14755,14 @@
         </is>
       </c>
       <c r="G397" s="2" t="n">
-        <v>0.057</v>
+        <v>0.352</v>
       </c>
       <c r="H397" s="3" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-345</t>
+          <t>PL-RT-371</t>
         </is>
       </c>
       <c r="B398" s="2" t="inlineStr">
@@ -14773,7 +14772,7 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 2.0 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 8 m/m2</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
@@ -14792,14 +14791,14 @@
         </is>
       </c>
       <c r="G398" s="2" t="n">
-        <v>0.004</v>
+        <v>0.016</v>
       </c>
       <c r="H398" s="3" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-359</t>
+          <t>PL-RT-378</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -14809,7 +14808,7 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 200 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 80 m/m2</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
@@ -14828,14 +14827,14 @@
         </is>
       </c>
       <c r="G399" s="2" t="n">
-        <v>0.065</v>
+        <v>0.053</v>
       </c>
       <c r="H399" s="3" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-350</t>
+          <t>PL-RT-389</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -14845,7 +14844,7 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 22 m/m2</t>
+          <t>３Ｃ XLPE 電力電纜 800 m/m2</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
@@ -14864,24 +14863,24 @@
         </is>
       </c>
       <c r="G400" s="2" t="n">
-        <v>0.015</v>
+        <v>0.395</v>
       </c>
       <c r="H400" s="3" t="n"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-360</t>
+          <t>PL-RT-278</t>
         </is>
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 250 m/m2</t>
+          <t>0.4m/m * 100P 數位電纜</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
@@ -14900,24 +14899,24 @@
         </is>
       </c>
       <c r="G401" s="2" t="n">
-        <v>0.075</v>
+        <v>0.035</v>
       </c>
       <c r="H401" s="3" t="n"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-346</t>
+          <t>PL-RT-279</t>
         </is>
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 3.5 m/m2</t>
+          <t>0.4m/m * 200P 數位電纜</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
@@ -14936,24 +14935,24 @@
         </is>
       </c>
       <c r="G402" s="2" t="n">
-        <v>0.005</v>
+        <v>0.055</v>
       </c>
       <c r="H402" s="3" t="n"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-351</t>
+          <t>PL-RT-280</t>
         </is>
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 30 m/m2</t>
+          <t>0.4m/m * 400P 數位電纜</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
@@ -14972,24 +14971,24 @@
         </is>
       </c>
       <c r="G403" s="2" t="n">
-        <v>0.018</v>
+        <v>0.075</v>
       </c>
       <c r="H403" s="3" t="n"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-361</t>
+          <t>PL-RT-288</t>
         </is>
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 325 m/m2</t>
+          <t>0.5m/m * 100P 數位電纜</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
@@ -15008,24 +15007,24 @@
         </is>
       </c>
       <c r="G404" s="2" t="n">
-        <v>0.117</v>
+        <v>0.04</v>
       </c>
       <c r="H404" s="3" t="n"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-352</t>
+          <t>PL-RT-284</t>
         </is>
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 38 m/m2</t>
+          <t>0.5m/m * 10P 數位電纜</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
@@ -15044,24 +15043,24 @@
         </is>
       </c>
       <c r="G405" s="2" t="n">
-        <v>0.021</v>
+        <v>0.01</v>
       </c>
       <c r="H405" s="3" t="n"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-362</t>
+          <t>PL-RT-289</t>
         </is>
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 400 m/m2</t>
+          <t>0.5m/m * 200P 數位電纜</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
@@ -15080,24 +15079,24 @@
         </is>
       </c>
       <c r="G406" s="2" t="n">
-        <v>0.128</v>
+        <v>0.06</v>
       </c>
       <c r="H406" s="3" t="n"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-347</t>
+          <t>PL-RT-285</t>
         </is>
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 5.5 m/m2</t>
+          <t>0.5m/m * 20P 數位電纜</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
@@ -15116,24 +15115,24 @@
         </is>
       </c>
       <c r="G407" s="2" t="n">
-        <v>0.008</v>
+        <v>0.015</v>
       </c>
       <c r="H407" s="3" t="n"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-353</t>
+          <t>PL-RT-281</t>
         </is>
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 50 m/m2</t>
+          <t>0.5m/m * 2P 數位電纜</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
@@ -15152,24 +15151,24 @@
         </is>
       </c>
       <c r="G408" s="2" t="n">
-        <v>0.023</v>
+        <v>0.003</v>
       </c>
       <c r="H408" s="3" t="n"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-363</t>
+          <t>PL-RT-290</t>
         </is>
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 500 m/m2</t>
+          <t>0.5m/m * 300P 數位電纜</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
@@ -15188,24 +15187,24 @@
         </is>
       </c>
       <c r="G409" s="2" t="n">
-        <v>0.154</v>
+        <v>0.075</v>
       </c>
       <c r="H409" s="3" t="n"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-354</t>
+          <t>PL-RT-286</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 60 m/m2</t>
+          <t>0.5m/m * 30P 數位電纜</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
@@ -15224,24 +15223,24 @@
         </is>
       </c>
       <c r="G410" s="2" t="n">
-        <v>0.029</v>
+        <v>0.02</v>
       </c>
       <c r="H410" s="3" t="n"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-364</t>
+          <t>PL-RT-291</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 600 m/m2</t>
+          <t>0.5m/m * 400P 數位電纜</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
@@ -15260,24 +15259,24 @@
         </is>
       </c>
       <c r="G411" s="2" t="n">
-        <v>0.185</v>
+        <v>0.09</v>
       </c>
       <c r="H411" s="3" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-365</t>
+          <t>PL-RT-282</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 725 m/m2</t>
+          <t>0.5m/m * 4P 數位電纜</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
@@ -15296,24 +15295,24 @@
         </is>
       </c>
       <c r="G412" s="2" t="n">
-        <v>0.22</v>
+        <v>0.005</v>
       </c>
       <c r="H412" s="3" t="n"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-348</t>
+          <t>PL-RT-287</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 8 m/m2</t>
+          <t>0.5m/m * 50P 數位電纜</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
@@ -15332,24 +15331,24 @@
         </is>
       </c>
       <c r="G413" s="2" t="n">
-        <v>0.01</v>
+        <v>0.035</v>
       </c>
       <c r="H413" s="3" t="n"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-355</t>
+          <t>PL-RT-283</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 80 m/m2</t>
+          <t>0.5m/m * 7P 數位電纜</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
@@ -15368,24 +15367,24 @@
         </is>
       </c>
       <c r="G414" s="2" t="n">
-        <v>0.035</v>
+        <v>0.007</v>
       </c>
       <c r="H414" s="3" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-366</t>
+          <t>PL-RT-292</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>１Ｃ XLPE 電力電纜 800 m/m2</t>
+          <t>３Ｃ２Ｖ同軸電纜</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
@@ -15404,24 +15403,24 @@
         </is>
       </c>
       <c r="G415" s="2" t="n">
-        <v>0.26</v>
+        <v>0.005</v>
       </c>
       <c r="H415" s="3" t="n"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-379</t>
+          <t>PL-RT-293</t>
         </is>
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 100 m/m2</t>
+          <t>５Ｃ２Ｖ同軸電纜</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
@@ -15440,24 +15439,24 @@
         </is>
       </c>
       <c r="G416" s="2" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.006</v>
       </c>
       <c r="H416" s="3" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-390</t>
+          <t>PL-RT-294</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>其他線材</t>
         </is>
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 1000 m/m2</t>
+          <t>７Ｃ２Ｖ同軸電纜</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
@@ -15476,24 +15475,24 @@
         </is>
       </c>
       <c r="G417" s="2" t="n">
-        <v>0.475</v>
+        <v>0.008</v>
       </c>
       <c r="H417" s="3" t="n"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-380</t>
+          <t>PL-RT-565</t>
         </is>
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 125 m/m2</t>
+          <t>W:1000mm * D:300mm</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
@@ -15508,28 +15507,28 @@
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G418" s="2" t="n">
-        <v>0.081</v>
+        <v>0.485</v>
       </c>
       <c r="H418" s="3" t="n"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-372</t>
+          <t>PL-RT-566</t>
         </is>
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 14 m/m2</t>
+          <t>W:1000mm * D:400mm</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
@@ -15544,28 +15543,28 @@
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G419" s="2" t="n">
-        <v>0.017</v>
+        <v>0.57</v>
       </c>
       <c r="H419" s="3" t="n"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-381</t>
+          <t>PL-RT-547</t>
         </is>
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 150 m/m2</t>
+          <t>W:100mm * D: 50mm</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
@@ -15580,28 +15579,28 @@
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G420" s="2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="H420" s="3" t="n"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-368</t>
+          <t>PL-RT-548</t>
         </is>
       </c>
       <c r="B421" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 2.0 m/m2</t>
+          <t>W:100mm * D:100mm</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
@@ -15616,28 +15615,28 @@
       </c>
       <c r="F421" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G421" s="2" t="n">
-        <v>0.007</v>
+        <v>0.08</v>
       </c>
       <c r="H421" s="3" t="n"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-382</t>
+          <t>PL-RT-549</t>
         </is>
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 200 m/m2</t>
+          <t>W:200mm * D: 50mm</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
@@ -15652,7 +15651,7 @@
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G422" s="2" t="n">
@@ -15663,17 +15662,17 @@
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-373</t>
+          <t>PL-RT-550</t>
         </is>
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 22 m/m2</t>
+          <t>W:200mm * D:100mm</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
@@ -15688,28 +15687,28 @@
       </c>
       <c r="F423" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G423" s="2" t="n">
-        <v>0.025</v>
+        <v>0.105</v>
       </c>
       <c r="H423" s="3" t="n"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-383</t>
+          <t>PL-RT-551</t>
         </is>
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 250 m/m2</t>
+          <t>W:300mm * D:100mm</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
@@ -15724,28 +15723,28 @@
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G424" s="2" t="n">
-        <v>0.112</v>
+        <v>0.115</v>
       </c>
       <c r="H424" s="3" t="n"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-369</t>
+          <t>PL-RT-552</t>
         </is>
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 3.5 m/m2</t>
+          <t>W:300mm * D:150mm</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
@@ -15760,28 +15759,28 @@
       </c>
       <c r="F425" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G425" s="2" t="n">
-        <v>0.008</v>
+        <v>0.125</v>
       </c>
       <c r="H425" s="3" t="n"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-374</t>
+          <t>PL-RT-553</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 30 m/m2</t>
+          <t>W:400mm * D:100mm</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
@@ -15796,28 +15795,28 @@
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G426" s="2" t="n">
-        <v>0.03</v>
+        <v>0.135</v>
       </c>
       <c r="H426" s="3" t="n"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-384</t>
+          <t>PL-RT-554</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 325 m/m2</t>
+          <t>W:400mm * D:150mm</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
@@ -15832,28 +15831,28 @@
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G427" s="2" t="n">
-        <v>0.16</v>
+        <v>0.145</v>
       </c>
       <c r="H427" s="3" t="n"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-375</t>
+          <t>PL-RT-555</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 38 m/m2</t>
+          <t>W:500mm * D:100mm</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
@@ -15868,28 +15867,28 @@
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G428" s="2" t="n">
-        <v>0.034</v>
+        <v>0.15</v>
       </c>
       <c r="H428" s="3" t="n"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-385</t>
+          <t>PL-RT-556</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 400 m/m2</t>
+          <t>W:500mm * D:200mm</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
@@ -15904,28 +15903,28 @@
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G429" s="2" t="n">
-        <v>0.211</v>
+        <v>0.165</v>
       </c>
       <c r="H429" s="3" t="n"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-370</t>
+          <t>PL-RT-557</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 5.5 m/m2</t>
+          <t>W:600mm * D:150mm</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
@@ -15940,28 +15939,28 @@
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G430" s="2" t="n">
-        <v>0.013</v>
+        <v>0.175</v>
       </c>
       <c r="H430" s="3" t="n"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-376</t>
+          <t>PL-RT-558</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 50 m/m2</t>
+          <t>W:600mm * D:200mm</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
@@ -15976,28 +15975,28 @@
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G431" s="2" t="n">
-        <v>0.038</v>
+        <v>0.188</v>
       </c>
       <c r="H431" s="3" t="n"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-386</t>
+          <t>PL-RT-559</t>
         </is>
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 500 m/m2</t>
+          <t>W:700mm * D:200mm</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
@@ -16012,28 +16011,28 @@
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G432" s="2" t="n">
-        <v>0.254</v>
+        <v>0.205</v>
       </c>
       <c r="H432" s="3" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-377</t>
+          <t>PL-RT-560</t>
         </is>
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 60 m/m2</t>
+          <t>W:700mm * D:300mm</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
@@ -16048,28 +16047,28 @@
       </c>
       <c r="F433" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G433" s="2" t="n">
-        <v>0.045</v>
+        <v>0.225</v>
       </c>
       <c r="H433" s="3" t="n"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-387</t>
+          <t>PL-RT-561</t>
         </is>
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 600 m/m2</t>
+          <t>W:800mm * D:200mm</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
@@ -16084,28 +16083,28 @@
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G434" s="2" t="n">
-        <v>0.285</v>
+        <v>0.245</v>
       </c>
       <c r="H434" s="3" t="n"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-388</t>
+          <t>PL-RT-562</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 725 m/m2</t>
+          <t>W:800mm * D:300mm</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
@@ -16120,28 +16119,28 @@
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G435" s="2" t="n">
-        <v>0.352</v>
+        <v>0.285</v>
       </c>
       <c r="H435" s="3" t="n"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-371</t>
+          <t>PL-RT-563</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 8 m/m2</t>
+          <t>W:900mm * D:300mm</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
@@ -16156,28 +16155,28 @@
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G436" s="2" t="n">
-        <v>0.016</v>
+        <v>0.356</v>
       </c>
       <c r="H436" s="3" t="n"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-378</t>
+          <t>PL-RT-564</t>
         </is>
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 80 m/m2</t>
+          <t>W:900mm * D:400mm</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
@@ -16192,28 +16191,28 @@
       </c>
       <c r="F437" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G437" s="2" t="n">
-        <v>0.053</v>
+        <v>0.456</v>
       </c>
       <c r="H437" s="3" t="n"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-389</t>
+          <t>PL-RT-576</t>
         </is>
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t>XLPE電纜</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ XLPE 電力電纜 800 m/m2</t>
+          <t>出線栓標誌銅蓋</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
@@ -16228,28 +16227,28 @@
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G438" s="2" t="n">
-        <v>0.395</v>
+        <v>0.05</v>
       </c>
       <c r="H438" s="3" t="n"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-278</t>
+          <t>PL-RT-570</t>
         </is>
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>0.4m/m * 100P 數位電纜</t>
+          <t>地板標誌蓋</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
@@ -16264,28 +16263,28 @@
       </c>
       <c r="F439" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G439" s="2" t="n">
-        <v>0.035</v>
+        <v>0.075</v>
       </c>
       <c r="H439" s="3" t="n"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-279</t>
+          <t>PL-RT-567</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>0.4m/m * 200P 數位電纜</t>
+          <t>地板線槽接線盒 34W*34H*5D CM</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
@@ -16300,28 +16299,28 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G440" s="2" t="n">
-        <v>0.055</v>
+        <v>0.16</v>
       </c>
       <c r="H440" s="3" t="n"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-280</t>
+          <t>PL-RT-579</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>0.4m/m * 400P 數位電纜</t>
+          <t>末端接頭 1"</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
@@ -16336,28 +16335,28 @@
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G441" s="2" t="n">
-        <v>0.075</v>
+        <v>0.09</v>
       </c>
       <c r="H441" s="3" t="n"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-288</t>
+          <t>PL-RT-577</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>0.5m/m * 100P 數位電纜</t>
+          <t>末端接頭 1/2"</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
@@ -16372,28 +16371,28 @@
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G442" s="2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H442" s="3" t="n"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-284</t>
+          <t>PL-RT-578</t>
         </is>
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>0.5m/m * 10P 數位電纜</t>
+          <t>末端接頭 3/4"</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
@@ -16408,28 +16407,28 @@
       </c>
       <c r="F443" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G443" s="2" t="n">
-        <v>0.01</v>
+        <v>0.075</v>
       </c>
       <c r="H443" s="3" t="n"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-289</t>
+          <t>PL-RT-574</t>
         </is>
       </c>
       <c r="B444" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>0.5m/m * 200P 數位電纜</t>
+          <t>末端蓋</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
@@ -16444,28 +16443,28 @@
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G444" s="2" t="n">
-        <v>0.06</v>
+        <v>0.038</v>
       </c>
       <c r="H444" s="3" t="n"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-285</t>
+          <t>PL-RT-575</t>
         </is>
       </c>
       <c r="B445" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>0.5m/m * 20P 數位電纜</t>
+          <t>線槽接頭</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
@@ -16480,28 +16479,28 @@
       </c>
       <c r="F445" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G445" s="2" t="n">
-        <v>0.015</v>
+        <v>0.075</v>
       </c>
       <c r="H445" s="3" t="n"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-281</t>
+          <t>PL-RT-571</t>
         </is>
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>0.5m/m * 2P 數位電纜</t>
+          <t>線槽支架</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
@@ -16516,28 +16515,28 @@
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G446" s="2" t="n">
-        <v>0.003</v>
+        <v>0.095</v>
       </c>
       <c r="H446" s="3" t="n"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-290</t>
+          <t>PL-RT-568</t>
         </is>
       </c>
       <c r="B447" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>0.5m/m * 300P 數位電纜</t>
+          <t>鋁合金地板線槽 5W*2.5H*1.8D CM</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
@@ -16552,28 +16551,28 @@
       </c>
       <c r="F447" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G447" s="2" t="n">
-        <v>0.075</v>
+        <v>0.125</v>
       </c>
       <c r="H447" s="3" t="n"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-286</t>
+          <t>PL-RT-569</t>
         </is>
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>0.5m/m * 30P 數位電纜</t>
+          <t>鍍鋅鋼板地板線槽 5W*2.5H*1.8D CM</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
@@ -16588,28 +16587,28 @@
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G448" s="2" t="n">
-        <v>0.02</v>
+        <v>0.145</v>
       </c>
       <c r="H448" s="3" t="n"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-291</t>
+          <t>PL-RT-573</t>
         </is>
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>0.5m/m * 400P 數位電纜</t>
+          <t>電力插座31φ2P 15A 125V+E</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
@@ -16624,28 +16623,28 @@
       </c>
       <c r="F449" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G449" s="2" t="n">
-        <v>0.09</v>
+        <v>0.175</v>
       </c>
       <c r="H449" s="3" t="n"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-282</t>
+          <t>PL-RT-572</t>
         </is>
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>線槽</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>0.5m/m * 4P 數位電纜</t>
+          <t>電話出線口31φ</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
@@ -16660,28 +16659,28 @@
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G450" s="2" t="n">
-        <v>0.005</v>
+        <v>0.175</v>
       </c>
       <c r="H450" s="3" t="n"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-287</t>
+          <t>PL-RT-407</t>
         </is>
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>0.5m/m * 50P 數位電纜</t>
+          <t>０．５ｍ／ｍ １００Ｐ</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
@@ -16700,24 +16699,24 @@
         </is>
       </c>
       <c r="G451" s="2" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="H451" s="3" t="n"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-283</t>
+          <t>PL-RT-399</t>
         </is>
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>0.5m/m * 7P 數位電纜</t>
+          <t>０．５ｍ／ｍ １０Ｐ</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
@@ -16736,24 +16735,24 @@
         </is>
       </c>
       <c r="G452" s="2" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="H452" s="3" t="n"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-292</t>
+          <t>PL-RT-400</t>
         </is>
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>３Ｃ２Ｖ同軸電纜</t>
+          <t>０．５ｍ／ｍ １２Ｐ</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
@@ -16772,24 +16771,24 @@
         </is>
       </c>
       <c r="G453" s="2" t="n">
-        <v>0.005</v>
+        <v>0.012</v>
       </c>
       <c r="H453" s="3" t="n"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-293</t>
+          <t>PL-RT-401</t>
         </is>
       </c>
       <c r="B454" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>５Ｃ２Ｖ同軸電纜</t>
+          <t>０．５ｍ／ｍ １５Ｐ</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -16808,24 +16807,24 @@
         </is>
       </c>
       <c r="G454" s="2" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="H454" s="3" t="n"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-294</t>
+          <t>PL-RT-402</t>
         </is>
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t>其他線材</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>７Ｃ２Ｖ同軸電纜</t>
+          <t>０．５ｍ／ｍ １８Ｐ</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
@@ -16844,24 +16843,24 @@
         </is>
       </c>
       <c r="G455" s="2" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="H455" s="3" t="n"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-565</t>
+          <t>PL-RT-408</t>
         </is>
       </c>
       <c r="B456" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>W:1000mm * D:300mm</t>
+          <t>０．５ｍ／ｍ ２００Ｐ</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -16876,28 +16875,28 @@
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G456" s="2" t="n">
-        <v>0.485</v>
+        <v>0.06</v>
       </c>
       <c r="H456" s="3" t="n"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-566</t>
+          <t>PL-RT-403</t>
         </is>
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>W:1000mm * D:400mm</t>
+          <t>０．５ｍ／ｍ ２０Ｐ</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
@@ -16912,28 +16911,28 @@
       </c>
       <c r="F457" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G457" s="2" t="n">
-        <v>0.57</v>
+        <v>0.015</v>
       </c>
       <c r="H457" s="3" t="n"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-547</t>
+          <t>PL-RT-404</t>
         </is>
       </c>
       <c r="B458" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>W:100mm * D: 50mm</t>
+          <t>０．５ｍ／ｍ ２４Ｐ</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
@@ -16948,28 +16947,28 @@
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G458" s="2" t="n">
-        <v>0.075</v>
+        <v>0.018</v>
       </c>
       <c r="H458" s="3" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-548</t>
+          <t>PL-RT-391</t>
         </is>
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>W:100mm * D:100mm</t>
+          <t>０．５ｍ／ｍ ２Ｃ</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
@@ -16984,28 +16983,28 @@
       </c>
       <c r="F459" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G459" s="2" t="n">
-        <v>0.08</v>
+        <v>0.0015</v>
       </c>
       <c r="H459" s="3" t="n"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-549</t>
+          <t>PL-RT-409</t>
         </is>
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>W:200mm * D: 50mm</t>
+          <t>０．５ｍ／ｍ ３００Ｐ</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
@@ -17020,28 +17019,28 @@
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G460" s="2" t="n">
-        <v>0.095</v>
+        <v>0.075</v>
       </c>
       <c r="H460" s="3" t="n"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-550</t>
+          <t>PL-RT-405</t>
         </is>
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>W:200mm * D:100mm</t>
+          <t>０．５ｍ／ｍ ３０Ｐ</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
@@ -17056,28 +17055,28 @@
       </c>
       <c r="F461" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G461" s="2" t="n">
-        <v>0.105</v>
+        <v>0.02</v>
       </c>
       <c r="H461" s="3" t="n"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-551</t>
+          <t>PL-RT-392</t>
         </is>
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>W:300mm * D:100mm</t>
+          <t>０．５ｍ／ｍ ３Ｃ</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
@@ -17092,28 +17091,28 @@
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G462" s="2" t="n">
-        <v>0.115</v>
+        <v>0.002</v>
       </c>
       <c r="H462" s="3" t="n"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-552</t>
+          <t>PL-RT-410</t>
         </is>
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>W:300mm * D:150mm</t>
+          <t>０．５ｍ／ｍ ４００Ｐ</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
@@ -17128,28 +17127,28 @@
       </c>
       <c r="F463" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G463" s="2" t="n">
-        <v>0.125</v>
+        <v>0.09</v>
       </c>
       <c r="H463" s="3" t="n"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-553</t>
+          <t>PL-RT-393</t>
         </is>
       </c>
       <c r="B464" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>W:400mm * D:100mm</t>
+          <t>０．５ｍ／ｍ ４Ｃ</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
@@ -17164,28 +17163,28 @@
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G464" s="2" t="n">
-        <v>0.135</v>
+        <v>0.002</v>
       </c>
       <c r="H464" s="3" t="n"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-554</t>
+          <t>PL-RT-406</t>
         </is>
       </c>
       <c r="B465" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>W:400mm * D:150mm</t>
+          <t>０．５ｍ／ｍ ５０Ｐ</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
@@ -17200,28 +17199,28 @@
       </c>
       <c r="F465" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G465" s="2" t="n">
-        <v>0.145</v>
+        <v>0.035</v>
       </c>
       <c r="H465" s="3" t="n"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-555</t>
+          <t>PL-RT-394</t>
         </is>
       </c>
       <c r="B466" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>W:500mm * D:100mm</t>
+          <t>０．５ｍ／ｍ ５Ｃ</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
@@ -17236,28 +17235,28 @@
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G466" s="2" t="n">
-        <v>0.15</v>
+        <v>0.003</v>
       </c>
       <c r="H466" s="3" t="n"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-556</t>
+          <t>PL-RT-398</t>
         </is>
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>W:500mm * D:200mm</t>
+          <t>０．５ｍ／ｍ ５Ｐ</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
@@ -17272,28 +17271,28 @@
       </c>
       <c r="F467" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G467" s="2" t="n">
-        <v>0.165</v>
+        <v>0.008</v>
       </c>
       <c r="H467" s="3" t="n"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-557</t>
+          <t>PL-RT-411</t>
         </is>
       </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>W:600mm * D:150mm</t>
+          <t>０．５ｍ／ｍ ６００Ｐ</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
@@ -17308,28 +17307,28 @@
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G468" s="2" t="n">
-        <v>0.175</v>
+        <v>0.126</v>
       </c>
       <c r="H468" s="3" t="n"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-558</t>
+          <t>PL-RT-395</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>W:600mm * D:200mm</t>
+          <t>０．５ｍ／ｍ ６Ｃ</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
@@ -17344,28 +17343,28 @@
       </c>
       <c r="F469" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G469" s="2" t="n">
-        <v>0.188</v>
+        <v>0.004</v>
       </c>
       <c r="H469" s="3" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-559</t>
+          <t>PL-RT-396</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>W:700mm * D:200mm</t>
+          <t>０．５ｍ／ｍ ８Ｃ</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
@@ -17380,28 +17379,28 @@
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G470" s="2" t="n">
-        <v>0.205</v>
+        <v>0.005</v>
       </c>
       <c r="H470" s="3" t="n"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-560</t>
+          <t>PL-RT-397</t>
         </is>
       </c>
       <c r="B471" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>W:700mm * D:300mm</t>
+          <t>０．５ｍ／ｍ ９Ｃ</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
@@ -17416,28 +17415,28 @@
       </c>
       <c r="F471" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G471" s="2" t="n">
-        <v>0.225</v>
+        <v>0.007</v>
       </c>
       <c r="H471" s="3" t="n"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-561</t>
+          <t>PL-RT-428</t>
         </is>
       </c>
       <c r="B472" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>W:800mm * D:200mm</t>
+          <t>０．６５ｍ／ｍ １００Ｐ</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
@@ -17452,28 +17451,28 @@
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G472" s="2" t="n">
-        <v>0.245</v>
+        <v>0.045</v>
       </c>
       <c r="H472" s="3" t="n"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-562</t>
+          <t>PL-RT-420</t>
         </is>
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>W:800mm * D:300mm</t>
+          <t>０．６５ｍ／ｍ １０Ｐ</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
@@ -17488,28 +17487,28 @@
       </c>
       <c r="F473" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G473" s="2" t="n">
-        <v>0.285</v>
+        <v>0.011</v>
       </c>
       <c r="H473" s="3" t="n"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-563</t>
+          <t>PL-RT-421</t>
         </is>
       </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>W:900mm * D:300mm</t>
+          <t>０．６５ｍ／ｍ １２Ｐ</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
@@ -17524,28 +17523,28 @@
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G474" s="2" t="n">
-        <v>0.356</v>
+        <v>0.013</v>
       </c>
       <c r="H474" s="3" t="n"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-564</t>
+          <t>PL-RT-422</t>
         </is>
       </c>
       <c r="B475" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>W:900mm * D:400mm</t>
+          <t>０．６５ｍ／ｍ １５Ｐ</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
@@ -17560,28 +17559,28 @@
       </c>
       <c r="F475" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G475" s="2" t="n">
-        <v>0.456</v>
+        <v>0.015</v>
       </c>
       <c r="H475" s="3" t="n"/>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-576</t>
+          <t>PL-RT-423</t>
         </is>
       </c>
       <c r="B476" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>出線栓標誌銅蓋</t>
+          <t>０．６５ｍ／ｍ １８Ｐ</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
@@ -17596,28 +17595,28 @@
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G476" s="2" t="n">
-        <v>0.05</v>
+        <v>0.016</v>
       </c>
       <c r="H476" s="3" t="n"/>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-570</t>
+          <t>PL-RT-429</t>
         </is>
       </c>
       <c r="B477" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>地板標誌蓋</t>
+          <t>０．６５ｍ／ｍ ２００Ｐ</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
@@ -17632,28 +17631,28 @@
       </c>
       <c r="F477" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G477" s="2" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H477" s="3" t="n"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-567</t>
+          <t>PL-RT-424</t>
         </is>
       </c>
       <c r="B478" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>地板線槽接線盒 34W*34H*5D CM</t>
+          <t>０．６５ｍ／ｍ ２０Ｐ</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
@@ -17668,28 +17667,28 @@
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G478" s="2" t="n">
-        <v>0.16</v>
+        <v>0.018</v>
       </c>
       <c r="H478" s="3" t="n"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-579</t>
+          <t>PL-RT-425</t>
         </is>
       </c>
       <c r="B479" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>末端接頭 1"</t>
+          <t>０．６５ｍ／ｍ ２４Ｐ</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
@@ -17704,28 +17703,28 @@
       </c>
       <c r="F479" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G479" s="2" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="H479" s="3" t="n"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-577</t>
+          <t>PL-RT-412</t>
         </is>
       </c>
       <c r="B480" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>末端接頭 1/2"</t>
+          <t>０．６５ｍ／ｍ ２Ｃ</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
@@ -17740,28 +17739,28 @@
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G480" s="2" t="n">
-        <v>0.06</v>
+        <v>0.002</v>
       </c>
       <c r="H480" s="3" t="n"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-578</t>
+          <t>PL-RT-430</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>末端接頭 3/4"</t>
+          <t>０．６５ｍ／ｍ ３００Ｐ</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
@@ -17776,28 +17775,28 @@
       </c>
       <c r="F481" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G481" s="2" t="n">
-        <v>0.075</v>
+        <v>0.082</v>
       </c>
       <c r="H481" s="3" t="n"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-574</t>
+          <t>PL-RT-426</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>末端蓋</t>
+          <t>０．６５ｍ／ｍ ３０Ｐ</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
@@ -17812,28 +17811,28 @@
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G482" s="2" t="n">
-        <v>0.038</v>
+        <v>0.023</v>
       </c>
       <c r="H482" s="3" t="n"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-575</t>
+          <t>PL-RT-413</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>線槽接頭</t>
+          <t>０．６５ｍ／ｍ ３Ｃ</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
@@ -17848,28 +17847,28 @@
       </c>
       <c r="F483" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G483" s="2" t="n">
-        <v>0.075</v>
+        <v>0.002</v>
       </c>
       <c r="H483" s="3" t="n"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-571</t>
+          <t>PL-RT-431</t>
         </is>
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>線槽支架</t>
+          <t>０．６５ｍ／ｍ ４００Ｐ</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
@@ -17884,28 +17883,28 @@
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G484" s="2" t="n">
-        <v>0.095</v>
+        <v>0.102</v>
       </c>
       <c r="H484" s="3" t="n"/>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-568</t>
+          <t>PL-RT-414</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>鋁合金地板線槽 5W*2.5H*1.8D CM</t>
+          <t>０．６５ｍ／ｍ ４Ｃ</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
@@ -17920,28 +17919,28 @@
       </c>
       <c r="F485" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G485" s="2" t="n">
-        <v>0.125</v>
+        <v>0.003</v>
       </c>
       <c r="H485" s="3" t="n"/>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-569</t>
+          <t>PL-RT-427</t>
         </is>
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>鍍鋅鋼板地板線槽 5W*2.5H*1.8D CM</t>
+          <t>０．６５ｍ／ｍ ５０Ｐ</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
@@ -17956,28 +17955,28 @@
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G486" s="2" t="n">
-        <v>0.145</v>
+        <v>0.04</v>
       </c>
       <c r="H486" s="3" t="n"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-573</t>
+          <t>PL-RT-415</t>
         </is>
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>電力插座31φ2P 15A 125V+E</t>
+          <t>０．６５ｍ／ｍ ５Ｃ</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
@@ -17992,28 +17991,28 @@
       </c>
       <c r="F487" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G487" s="2" t="n">
-        <v>0.175</v>
+        <v>0.004</v>
       </c>
       <c r="H487" s="3" t="n"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-572</t>
+          <t>PL-RT-419</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t>線槽</t>
+          <t>通信電纜線</t>
         </is>
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>電話出線口31φ</t>
+          <t>０．６５ｍ／ｍ ５Ｐ</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
@@ -18028,18 +18027,18 @@
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>管內</t>
         </is>
       </c>
       <c r="G488" s="2" t="n">
-        <v>0.175</v>
+        <v>0.008</v>
       </c>
       <c r="H488" s="3" t="n"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-407</t>
+          <t>PL-RT-432</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
@@ -18049,7 +18048,7 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ １００Ｐ</t>
+          <t>０．６５ｍ／ｍ ６００Ｐ</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
@@ -18068,14 +18067,14 @@
         </is>
       </c>
       <c r="G489" s="2" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H489" s="3" t="n"/>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-399</t>
+          <t>PL-RT-416</t>
         </is>
       </c>
       <c r="B490" s="2" t="inlineStr">
@@ -18085,7 +18084,7 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ １０Ｐ</t>
+          <t>０．６５ｍ／ｍ ６Ｃ</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
@@ -18104,14 +18103,14 @@
         </is>
       </c>
       <c r="G490" s="2" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="H490" s="3" t="n"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-400</t>
+          <t>PL-RT-417</t>
         </is>
       </c>
       <c r="B491" s="2" t="inlineStr">
@@ -18121,7 +18120,7 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ １２Ｐ</t>
+          <t>０．６５ｍ／ｍ ８Ｃ</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
@@ -18140,14 +18139,14 @@
         </is>
       </c>
       <c r="G491" s="2" t="n">
-        <v>0.012</v>
+        <v>0.006</v>
       </c>
       <c r="H491" s="3" t="n"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-401</t>
+          <t>PL-RT-418</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
@@ -18157,7 +18156,7 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ １５Ｐ</t>
+          <t>０．６５ｍ／ｍ ９Ｃ</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
@@ -18176,14 +18175,14 @@
         </is>
       </c>
       <c r="G492" s="2" t="n">
-        <v>0.013</v>
+        <v>0.007</v>
       </c>
       <c r="H492" s="3" t="n"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-402</t>
+          <t>PL-RT-449</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
@@ -18193,7 +18192,7 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ １８Ｐ</t>
+          <t>０．９ｍ／ｍ １００Ｐ</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
@@ -18212,14 +18211,14 @@
         </is>
       </c>
       <c r="G493" s="2" t="n">
-        <v>0.014</v>
+        <v>0.05</v>
       </c>
       <c r="H493" s="3" t="n"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-408</t>
+          <t>PL-RT-441</t>
         </is>
       </c>
       <c r="B494" s="2" t="inlineStr">
@@ -18229,7 +18228,7 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ２００Ｐ</t>
+          <t>０．９ｍ／ｍ １０Ｐ</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
@@ -18248,14 +18247,14 @@
         </is>
       </c>
       <c r="G494" s="2" t="n">
-        <v>0.06</v>
+        <v>0.013</v>
       </c>
       <c r="H494" s="3" t="n"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-403</t>
+          <t>PL-RT-442</t>
         </is>
       </c>
       <c r="B495" s="2" t="inlineStr">
@@ -18265,7 +18264,7 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ２０Ｐ</t>
+          <t>０．９ｍ／ｍ １２Ｐ</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
@@ -18284,14 +18283,14 @@
         </is>
       </c>
       <c r="G495" s="2" t="n">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="H495" s="3" t="n"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-404</t>
+          <t>PL-RT-443</t>
         </is>
       </c>
       <c r="B496" s="2" t="inlineStr">
@@ -18301,7 +18300,7 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ２４Ｐ</t>
+          <t>０．９ｍ／ｍ １５Ｐ</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
@@ -18320,14 +18319,14 @@
         </is>
       </c>
       <c r="G496" s="2" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="H496" s="3" t="n"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-391</t>
+          <t>PL-RT-444</t>
         </is>
       </c>
       <c r="B497" s="2" t="inlineStr">
@@ -18337,7 +18336,7 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ２Ｃ</t>
+          <t>０．９ｍ／ｍ １８Ｐ</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
@@ -18356,14 +18355,14 @@
         </is>
       </c>
       <c r="G497" s="2" t="n">
-        <v>0.0015</v>
+        <v>0.018</v>
       </c>
       <c r="H497" s="3" t="n"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-409</t>
+          <t>PL-RT-450</t>
         </is>
       </c>
       <c r="B498" s="2" t="inlineStr">
@@ -18373,7 +18372,7 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ３００Ｐ</t>
+          <t>０．９ｍ／ｍ ２００Ｐ</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
@@ -18399,7 +18398,7 @@
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-405</t>
+          <t>PL-RT-445</t>
         </is>
       </c>
       <c r="B499" s="2" t="inlineStr">
@@ -18409,7 +18408,7 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ３０Ｐ</t>
+          <t>０．９ｍ／ｍ ２０Ｐ</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
@@ -18435,7 +18434,7 @@
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-392</t>
+          <t>PL-RT-446</t>
         </is>
       </c>
       <c r="B500" s="2" t="inlineStr">
@@ -18445,7 +18444,7 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ３Ｃ</t>
+          <t>０．９ｍ／ｍ ２４Ｐ</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
@@ -18464,14 +18463,14 @@
         </is>
       </c>
       <c r="G500" s="2" t="n">
-        <v>0.002</v>
+        <v>0.022</v>
       </c>
       <c r="H500" s="3" t="n"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-410</t>
+          <t>PL-RT-433</t>
         </is>
       </c>
       <c r="B501" s="2" t="inlineStr">
@@ -18481,7 +18480,7 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ４００Ｐ</t>
+          <t>０．９ｍ／ｍ ２Ｃ</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
@@ -18500,14 +18499,14 @@
         </is>
       </c>
       <c r="G501" s="2" t="n">
-        <v>0.09</v>
+        <v>0.004</v>
       </c>
       <c r="H501" s="3" t="n"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-393</t>
+          <t>PL-RT-451</t>
         </is>
       </c>
       <c r="B502" s="2" t="inlineStr">
@@ -18517,7 +18516,7 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ４Ｃ</t>
+          <t>０．９ｍ／ｍ ３００Ｐ</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
@@ -18536,14 +18535,14 @@
         </is>
       </c>
       <c r="G502" s="2" t="n">
-        <v>0.002</v>
+        <v>0.09</v>
       </c>
       <c r="H502" s="3" t="n"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-406</t>
+          <t>PL-RT-447</t>
         </is>
       </c>
       <c r="B503" s="2" t="inlineStr">
@@ -18553,7 +18552,7 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ５０Ｐ</t>
+          <t>０．９ｍ／ｍ ３０Ｐ</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
@@ -18572,14 +18571,14 @@
         </is>
       </c>
       <c r="G503" s="2" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="H503" s="3" t="n"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-394</t>
+          <t>PL-RT-434</t>
         </is>
       </c>
       <c r="B504" s="2" t="inlineStr">
@@ -18589,7 +18588,7 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ５Ｃ</t>
+          <t>０．９ｍ／ｍ ３Ｃ</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
@@ -18608,14 +18607,14 @@
         </is>
       </c>
       <c r="G504" s="2" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="H504" s="3" t="n"/>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-398</t>
+          <t>PL-RT-452</t>
         </is>
       </c>
       <c r="B505" s="2" t="inlineStr">
@@ -18625,7 +18624,7 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ５Ｐ</t>
+          <t>０．９ｍ／ｍ ４００Ｐ</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
@@ -18644,14 +18643,14 @@
         </is>
       </c>
       <c r="G505" s="2" t="n">
-        <v>0.008</v>
+        <v>0.11</v>
       </c>
       <c r="H505" s="3" t="n"/>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-411</t>
+          <t>PL-RT-435</t>
         </is>
       </c>
       <c r="B506" s="2" t="inlineStr">
@@ -18661,7 +18660,7 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ６００Ｐ</t>
+          <t>０．９ｍ／ｍ ４Ｃ</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
@@ -18680,14 +18679,14 @@
         </is>
       </c>
       <c r="G506" s="2" t="n">
-        <v>0.126</v>
+        <v>0.006</v>
       </c>
       <c r="H506" s="3" t="n"/>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-395</t>
+          <t>PL-RT-448</t>
         </is>
       </c>
       <c r="B507" s="2" t="inlineStr">
@@ -18697,7 +18696,7 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ６Ｃ</t>
+          <t>０．９ｍ／ｍ ５０Ｐ</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
@@ -18716,14 +18715,14 @@
         </is>
       </c>
       <c r="G507" s="2" t="n">
-        <v>0.004</v>
+        <v>0.045</v>
       </c>
       <c r="H507" s="3" t="n"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-396</t>
+          <t>PL-RT-436</t>
         </is>
       </c>
       <c r="B508" s="2" t="inlineStr">
@@ -18733,7 +18732,7 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ８Ｃ</t>
+          <t>０．９ｍ／ｍ ５Ｃ</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
@@ -18752,14 +18751,14 @@
         </is>
       </c>
       <c r="G508" s="2" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="H508" s="3" t="n"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-397</t>
+          <t>PL-RT-440</t>
         </is>
       </c>
       <c r="B509" s="2" t="inlineStr">
@@ -18769,7 +18768,7 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>０．５ｍ／ｍ ９Ｃ</t>
+          <t>０．９ｍ／ｍ ５Ｐ</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
@@ -18788,14 +18787,14 @@
         </is>
       </c>
       <c r="G509" s="2" t="n">
-        <v>0.007</v>
+        <v>0.011</v>
       </c>
       <c r="H509" s="3" t="n"/>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-428</t>
+          <t>PL-RT-453</t>
         </is>
       </c>
       <c r="B510" s="2" t="inlineStr">
@@ -18805,7 +18804,7 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ １００Ｐ</t>
+          <t>０．９ｍ／ｍ ６００Ｐ</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
@@ -18824,14 +18823,14 @@
         </is>
       </c>
       <c r="G510" s="2" t="n">
-        <v>0.045</v>
+        <v>0.135</v>
       </c>
       <c r="H510" s="3" t="n"/>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-420</t>
+          <t>PL-RT-437</t>
         </is>
       </c>
       <c r="B511" s="2" t="inlineStr">
@@ -18841,7 +18840,7 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ １０Ｐ</t>
+          <t>０．９ｍ／ｍ ６Ｃ</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
@@ -18860,14 +18859,14 @@
         </is>
       </c>
       <c r="G511" s="2" t="n">
-        <v>0.011</v>
+        <v>0.008</v>
       </c>
       <c r="H511" s="3" t="n"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-421</t>
+          <t>PL-RT-438</t>
         </is>
       </c>
       <c r="B512" s="2" t="inlineStr">
@@ -18877,7 +18876,7 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ １２Ｐ</t>
+          <t>０．９ｍ／ｍ ８Ｃ</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
@@ -18896,14 +18895,14 @@
         </is>
       </c>
       <c r="G512" s="2" t="n">
-        <v>0.013</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H512" s="3" t="n"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-422</t>
+          <t>PL-RT-439</t>
         </is>
       </c>
       <c r="B513" s="2" t="inlineStr">
@@ -18913,7 +18912,7 @@
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ １５Ｐ</t>
+          <t>０．９ｍ／ｍ ９Ｃ</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
@@ -18932,29 +18931,29 @@
         </is>
       </c>
       <c r="G513" s="2" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="H513" s="3" t="n"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-423</t>
+          <t>PL-RT-604</t>
         </is>
       </c>
       <c r="B514" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜終端頭</t>
         </is>
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ １８Ｐ</t>
+          <t>3C 14m/m2以下</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
@@ -18964,33 +18963,33 @@
       </c>
       <c r="F514" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G514" s="2" t="n">
-        <v>0.016</v>
+        <v>0.38</v>
       </c>
       <c r="H514" s="3" t="n"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-429</t>
+          <t>PL-RT-608</t>
         </is>
       </c>
       <c r="B515" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜終端頭</t>
         </is>
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ２００Ｐ</t>
+          <t>3C 150m/m2</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
@@ -19000,33 +18999,33 @@
       </c>
       <c r="F515" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G515" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.555</v>
       </c>
       <c r="H515" s="3" t="n"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-424</t>
+          <t>PL-RT-609</t>
         </is>
       </c>
       <c r="B516" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜終端頭</t>
         </is>
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ２０Ｐ</t>
+          <t>3C 200m/m2以上</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -19036,33 +19035,33 @@
       </c>
       <c r="F516" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G516" s="2" t="n">
-        <v>0.018</v>
+        <v>1.81</v>
       </c>
       <c r="H516" s="3" t="n"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-425</t>
+          <t>PL-RT-605</t>
         </is>
       </c>
       <c r="B517" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜終端頭</t>
         </is>
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ２４Ｐ</t>
+          <t>3C 22-38m/m2</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
@@ -19072,33 +19071,33 @@
       </c>
       <c r="F517" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G517" s="2" t="n">
-        <v>0.02</v>
+        <v>0.48</v>
       </c>
       <c r="H517" s="3" t="n"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-412</t>
+          <t>PL-RT-606</t>
         </is>
       </c>
       <c r="B518" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜終端頭</t>
         </is>
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ２Ｃ</t>
+          <t>3C 50-60m/m2</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
@@ -19108,33 +19107,33 @@
       </c>
       <c r="F518" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G518" s="2" t="n">
-        <v>0.002</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H518" s="3" t="n"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-430</t>
+          <t>PL-RT-607</t>
         </is>
       </c>
       <c r="B519" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜終端頭</t>
         </is>
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ３００Ｐ</t>
+          <t>3C 80-100m/m2</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
@@ -19144,28 +19143,28 @@
       </c>
       <c r="F519" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G519" s="2" t="n">
-        <v>0.082</v>
+        <v>0.91</v>
       </c>
       <c r="H519" s="3" t="n"/>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-426</t>
+          <t>PL-RT-537</t>
         </is>
       </c>
       <c r="B520" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ３０Ｐ</t>
+          <t>2MM(厚度) 伸縮直式電纜線架 1000W</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
@@ -19180,28 +19179,28 @@
       </c>
       <c r="F520" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G520" s="2" t="n">
-        <v>0.023</v>
+        <v>0.287</v>
       </c>
       <c r="H520" s="3" t="n"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-413</t>
+          <t>PL-RT-529</t>
         </is>
       </c>
       <c r="B521" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ３Ｃ</t>
+          <t>2MM(厚度) 伸縮直式電纜線架 200W</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
@@ -19216,28 +19215,28 @@
       </c>
       <c r="F521" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G521" s="2" t="n">
-        <v>0.002</v>
+        <v>0.125</v>
       </c>
       <c r="H521" s="3" t="n"/>
     </row>
     <row r="522">
       <c r="A522" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-431</t>
+          <t>PL-RT-530</t>
         </is>
       </c>
       <c r="B522" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ４００Ｐ</t>
+          <t>2MM(厚度) 伸縮直式電纜線架 300W</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
@@ -19252,28 +19251,28 @@
       </c>
       <c r="F522" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G522" s="2" t="n">
-        <v>0.102</v>
+        <v>0.145</v>
       </c>
       <c r="H522" s="3" t="n"/>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-414</t>
+          <t>PL-RT-531</t>
         </is>
       </c>
       <c r="B523" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ４Ｃ</t>
+          <t>2MM(厚度) 伸縮直式電纜線架 400W</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
@@ -19288,28 +19287,28 @@
       </c>
       <c r="F523" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G523" s="2" t="n">
-        <v>0.003</v>
+        <v>0.165</v>
       </c>
       <c r="H523" s="3" t="n"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-427</t>
+          <t>PL-RT-532</t>
         </is>
       </c>
       <c r="B524" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ５０Ｐ</t>
+          <t>2MM(厚度) 伸縮直式電纜線架 500W</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
@@ -19324,28 +19323,28 @@
       </c>
       <c r="F524" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G524" s="2" t="n">
-        <v>0.04</v>
+        <v>0.185</v>
       </c>
       <c r="H524" s="3" t="n"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-415</t>
+          <t>PL-RT-533</t>
         </is>
       </c>
       <c r="B525" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ５Ｃ</t>
+          <t>2MM(厚度) 伸縮直式電纜線架 600W</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
@@ -19360,28 +19359,28 @@
       </c>
       <c r="F525" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G525" s="2" t="n">
-        <v>0.004</v>
+        <v>0.195</v>
       </c>
       <c r="H525" s="3" t="n"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-419</t>
+          <t>PL-RT-534</t>
         </is>
       </c>
       <c r="B526" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ５Ｐ</t>
+          <t>2MM(厚度) 伸縮直式電纜線架 700W</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
@@ -19396,28 +19395,28 @@
       </c>
       <c r="F526" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G526" s="2" t="n">
-        <v>0.008</v>
+        <v>0.215</v>
       </c>
       <c r="H526" s="3" t="n"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-432</t>
+          <t>PL-RT-535</t>
         </is>
       </c>
       <c r="B527" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ６００Ｐ</t>
+          <t>2MM(厚度) 伸縮直式電纜線架 800W</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
@@ -19432,28 +19431,28 @@
       </c>
       <c r="F527" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G527" s="2" t="n">
-        <v>0.12</v>
+        <v>0.225</v>
       </c>
       <c r="H527" s="3" t="n"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-416</t>
+          <t>PL-RT-536</t>
         </is>
       </c>
       <c r="B528" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ６Ｃ</t>
+          <t>2MM(厚度) 伸縮直式電纜線架 900W</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
@@ -19468,28 +19467,28 @@
       </c>
       <c r="F528" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G528" s="2" t="n">
-        <v>0.005</v>
+        <v>0.249</v>
       </c>
       <c r="H528" s="3" t="n"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-417</t>
+          <t>PL-RT-546</t>
         </is>
       </c>
       <c r="B529" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ８Ｃ</t>
+          <t>3MM(厚度) 伸縮直式電纜線架 1000W</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
@@ -19504,28 +19503,28 @@
       </c>
       <c r="F529" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G529" s="2" t="n">
-        <v>0.006</v>
+        <v>0.305</v>
       </c>
       <c r="H529" s="3" t="n"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-418</t>
+          <t>PL-RT-538</t>
         </is>
       </c>
       <c r="B530" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>０．６５ｍ／ｍ ９Ｃ</t>
+          <t>3MM(厚度) 伸縮直式電纜線架 200W</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
@@ -19540,28 +19539,28 @@
       </c>
       <c r="F530" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G530" s="2" t="n">
-        <v>0.007</v>
+        <v>0.135</v>
       </c>
       <c r="H530" s="3" t="n"/>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-449</t>
+          <t>PL-RT-539</t>
         </is>
       </c>
       <c r="B531" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ １００Ｐ</t>
+          <t>3MM(厚度) 伸縮直式電纜線架 300W</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
@@ -19576,28 +19575,28 @@
       </c>
       <c r="F531" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G531" s="2" t="n">
-        <v>0.05</v>
+        <v>0.155</v>
       </c>
       <c r="H531" s="3" t="n"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-441</t>
+          <t>PL-RT-540</t>
         </is>
       </c>
       <c r="B532" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ １０Ｐ</t>
+          <t>3MM(厚度) 伸縮直式電纜線架 400W</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
@@ -19612,28 +19611,28 @@
       </c>
       <c r="F532" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G532" s="2" t="n">
-        <v>0.013</v>
+        <v>0.173</v>
       </c>
       <c r="H532" s="3" t="n"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-442</t>
+          <t>PL-RT-541</t>
         </is>
       </c>
       <c r="B533" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ １２Ｐ</t>
+          <t>3MM(厚度) 伸縮直式電纜線架 500W</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
@@ -19648,28 +19647,28 @@
       </c>
       <c r="F533" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G533" s="2" t="n">
-        <v>0.014</v>
+        <v>0.195</v>
       </c>
       <c r="H533" s="3" t="n"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-443</t>
+          <t>PL-RT-542</t>
         </is>
       </c>
       <c r="B534" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ １５Ｐ</t>
+          <t>3MM(厚度) 伸縮直式電纜線架 600W</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
@@ -19684,28 +19683,28 @@
       </c>
       <c r="F534" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G534" s="2" t="n">
-        <v>0.017</v>
+        <v>0.205</v>
       </c>
       <c r="H534" s="3" t="n"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-444</t>
+          <t>PL-RT-543</t>
         </is>
       </c>
       <c r="B535" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ １８Ｐ</t>
+          <t>3MM(厚度) 伸縮直式電纜線架 700W</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
@@ -19720,28 +19719,28 @@
       </c>
       <c r="F535" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G535" s="2" t="n">
-        <v>0.018</v>
+        <v>0.225</v>
       </c>
       <c r="H535" s="3" t="n"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-450</t>
+          <t>PL-RT-544</t>
         </is>
       </c>
       <c r="B536" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ２００Ｐ</t>
+          <t>3MM(厚度) 伸縮直式電纜線架 800W</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
@@ -19756,28 +19755,28 @@
       </c>
       <c r="F536" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G536" s="2" t="n">
-        <v>0.075</v>
+        <v>0.235</v>
       </c>
       <c r="H536" s="3" t="n"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-445</t>
+          <t>PL-RT-545</t>
         </is>
       </c>
       <c r="B537" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜線架</t>
         </is>
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ２０Ｐ</t>
+          <t>3MM(厚度) 伸縮直式電纜線架 900W</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
@@ -19792,33 +19791,33 @@
       </c>
       <c r="F537" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G537" s="2" t="n">
-        <v>0.02</v>
+        <v>0.265</v>
       </c>
       <c r="H537" s="3" t="n"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-446</t>
+          <t>PL-RT-592</t>
         </is>
       </c>
       <c r="B538" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ２４Ｐ</t>
+          <t>2MM預鑄式 15KV 125m/m2-150m/m2</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E538" s="2" t="inlineStr">
@@ -19828,33 +19827,33 @@
       </c>
       <c r="F538" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G538" s="2" t="n">
-        <v>0.022</v>
+        <v>0.471</v>
       </c>
       <c r="H538" s="3" t="n"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-433</t>
+          <t>PL-RT-593</t>
         </is>
       </c>
       <c r="B539" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ２Ｃ</t>
+          <t>2MM預鑄式 15KV 200m/m2</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E539" s="2" t="inlineStr">
@@ -19864,33 +19863,33 @@
       </c>
       <c r="F539" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G539" s="2" t="n">
-        <v>0.004</v>
+        <v>0.533</v>
       </c>
       <c r="H539" s="3" t="n"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-451</t>
+          <t>PL-RT-588</t>
         </is>
       </c>
       <c r="B540" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ３００Ｐ</t>
+          <t>2MM預鑄式 15KV 22m/m2以下</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr">
@@ -19900,33 +19899,33 @@
       </c>
       <c r="F540" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G540" s="2" t="n">
-        <v>0.09</v>
+        <v>0.282</v>
       </c>
       <c r="H540" s="3" t="n"/>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-447</t>
+          <t>PL-RT-594</t>
         </is>
       </c>
       <c r="B541" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C541" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ３０Ｐ</t>
+          <t>2MM預鑄式 15KV 250m/m2</t>
         </is>
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E541" s="2" t="inlineStr">
@@ -19936,33 +19935,33 @@
       </c>
       <c r="F541" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G541" s="2" t="n">
-        <v>0.03</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H541" s="3" t="n"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-434</t>
+          <t>PL-RT-589</t>
         </is>
       </c>
       <c r="B542" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C542" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ３Ｃ</t>
+          <t>2MM預鑄式 15KV 30m/m2-38m/m2</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E542" s="2" t="inlineStr">
@@ -19972,33 +19971,33 @@
       </c>
       <c r="F542" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G542" s="2" t="n">
-        <v>0.005</v>
+        <v>0.329</v>
       </c>
       <c r="H542" s="3" t="n"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-452</t>
+          <t>PL-RT-595</t>
         </is>
       </c>
       <c r="B543" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C543" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ４００Ｐ</t>
+          <t>2MM預鑄式 15KV 325m/m2</t>
         </is>
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E543" s="2" t="inlineStr">
@@ -20008,33 +20007,33 @@
       </c>
       <c r="F543" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G543" s="2" t="n">
-        <v>0.11</v>
+        <v>0.628</v>
       </c>
       <c r="H543" s="3" t="n"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-435</t>
+          <t>PL-RT-590</t>
         </is>
       </c>
       <c r="B544" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C544" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ４Ｃ</t>
+          <t>2MM預鑄式 15KV 50m/m2-60m/m2</t>
         </is>
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E544" s="2" t="inlineStr">
@@ -20044,33 +20043,33 @@
       </c>
       <c r="F544" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G544" s="2" t="n">
-        <v>0.006</v>
+        <v>0.393</v>
       </c>
       <c r="H544" s="3" t="n"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-448</t>
+          <t>PL-RT-591</t>
         </is>
       </c>
       <c r="B545" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C545" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ５０Ｐ</t>
+          <t>2MM預鑄式 15KV 80m/m2-100m/m2</t>
         </is>
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E545" s="2" t="inlineStr">
@@ -20080,33 +20079,33 @@
       </c>
       <c r="F545" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G545" s="2" t="n">
-        <v>0.045</v>
+        <v>0.44</v>
       </c>
       <c r="H545" s="3" t="n"/>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-436</t>
+          <t>PL-RT-600</t>
         </is>
       </c>
       <c r="B546" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C546" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ５Ｃ</t>
+          <t>2MM預鑄式 25KV 125m/m2-150m/m2</t>
         </is>
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E546" s="2" t="inlineStr">
@@ -20116,33 +20115,33 @@
       </c>
       <c r="F546" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G546" s="2" t="n">
-        <v>0.007</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H546" s="3" t="n"/>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-440</t>
+          <t>PL-RT-601</t>
         </is>
       </c>
       <c r="B547" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C547" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ５Ｐ</t>
+          <t>2MM預鑄式 25KV 200m/m2</t>
         </is>
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E547" s="2" t="inlineStr">
@@ -20152,33 +20151,33 @@
       </c>
       <c r="F547" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G547" s="2" t="n">
-        <v>0.011</v>
+        <v>0.628</v>
       </c>
       <c r="H547" s="3" t="n"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-453</t>
+          <t>PL-RT-596</t>
         </is>
       </c>
       <c r="B548" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C548" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ６００Ｐ</t>
+          <t>2MM預鑄式 25KV 22m/m2以下</t>
         </is>
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E548" s="2" t="inlineStr">
@@ -20188,33 +20187,33 @@
       </c>
       <c r="F548" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G548" s="2" t="n">
-        <v>0.135</v>
+        <v>0.314</v>
       </c>
       <c r="H548" s="3" t="n"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-437</t>
+          <t>PL-RT-602</t>
         </is>
       </c>
       <c r="B549" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C549" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ６Ｃ</t>
+          <t>2MM預鑄式 25KV 250m/m2</t>
         </is>
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E549" s="2" t="inlineStr">
@@ -20224,33 +20223,33 @@
       </c>
       <c r="F549" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G549" s="2" t="n">
-        <v>0.008</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H549" s="3" t="n"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-438</t>
+          <t>PL-RT-597</t>
         </is>
       </c>
       <c r="B550" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C550" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ８Ｃ</t>
+          <t>2MM預鑄式 25KV 30m/m2-38m/m2</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E550" s="2" t="inlineStr">
@@ -20260,33 +20259,33 @@
       </c>
       <c r="F550" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G550" s="2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.376</v>
       </c>
       <c r="H550" s="3" t="n"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-439</t>
+          <t>PL-RT-603</t>
         </is>
       </c>
       <c r="B551" s="2" t="inlineStr">
         <is>
-          <t>通信電纜線</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C551" s="2" t="inlineStr">
         <is>
-          <t>０．９ｍ／ｍ ９Ｃ</t>
+          <t>2MM預鑄式 25KV 325m/m2</t>
         </is>
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E551" s="2" t="inlineStr">
@@ -20296,28 +20295,28 @@
       </c>
       <c r="F551" s="2" t="inlineStr">
         <is>
-          <t>管內</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G551" s="2" t="n">
-        <v>0.01</v>
+        <v>0.754</v>
       </c>
       <c r="H551" s="3" t="n"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-604</t>
+          <t>PL-RT-598</t>
         </is>
       </c>
       <c r="B552" s="2" t="inlineStr">
         <is>
-          <t>電纜終端頭</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C552" s="2" t="inlineStr">
         <is>
-          <t>3C 14m/m2以下</t>
+          <t>2MM預鑄式 25KV 50m/m2-60m/m2</t>
         </is>
       </c>
       <c r="D552" s="2" t="inlineStr">
@@ -20336,24 +20335,24 @@
         </is>
       </c>
       <c r="G552" s="2" t="n">
-        <v>0.38</v>
+        <v>0.455</v>
       </c>
       <c r="H552" s="3" t="n"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-608</t>
+          <t>PL-RT-599</t>
         </is>
       </c>
       <c r="B553" s="2" t="inlineStr">
         <is>
-          <t>電纜終端頭</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C553" s="2" t="inlineStr">
         <is>
-          <t>3C 150m/m2</t>
+          <t>2MM預鑄式 25KV 80m/m2-100m/m2</t>
         </is>
       </c>
       <c r="D553" s="2" t="inlineStr">
@@ -20372,24 +20371,24 @@
         </is>
       </c>
       <c r="G553" s="2" t="n">
-        <v>1.555</v>
+        <v>0.502</v>
       </c>
       <c r="H553" s="3" t="n"/>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-609</t>
+          <t>PL-RT-584</t>
         </is>
       </c>
       <c r="B554" s="2" t="inlineStr">
         <is>
-          <t>電纜終端頭</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>3C 200m/m2以上</t>
+          <t>2MM預鑄式 6.6KV以下 125m/m2-150m/m2</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
@@ -20408,24 +20407,24 @@
         </is>
       </c>
       <c r="G554" s="2" t="n">
-        <v>1.81</v>
+        <v>0.345</v>
       </c>
       <c r="H554" s="3" t="n"/>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-605</t>
+          <t>PL-RT-585</t>
         </is>
       </c>
       <c r="B555" s="2" t="inlineStr">
         <is>
-          <t>電纜終端頭</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C555" s="2" t="inlineStr">
         <is>
-          <t>3C 22-38m/m2</t>
+          <t>2MM預鑄式 6.6KV以下 200m/m2</t>
         </is>
       </c>
       <c r="D555" s="2" t="inlineStr">
@@ -20444,24 +20443,24 @@
         </is>
       </c>
       <c r="G555" s="2" t="n">
-        <v>0.48</v>
+        <v>0.376</v>
       </c>
       <c r="H555" s="3" t="n"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-606</t>
+          <t>PL-RT-580</t>
         </is>
       </c>
       <c r="B556" s="2" t="inlineStr">
         <is>
-          <t>電纜終端頭</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C556" s="2" t="inlineStr">
         <is>
-          <t>3C 50-60m/m2</t>
+          <t>2MM預鑄式 6.6KV以下 22m/m2以下</t>
         </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
@@ -20480,24 +20479,24 @@
         </is>
       </c>
       <c r="G556" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.251</v>
       </c>
       <c r="H556" s="3" t="n"/>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-607</t>
+          <t>PL-RT-586</t>
         </is>
       </c>
       <c r="B557" s="2" t="inlineStr">
         <is>
-          <t>電纜終端頭</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C557" s="2" t="inlineStr">
         <is>
-          <t>3C 80-100m/m2</t>
+          <t>2MM預鑄式 6.6KV以下 250m/m2</t>
         </is>
       </c>
       <c r="D557" s="2" t="inlineStr">
@@ -20516,29 +20515,29 @@
         </is>
       </c>
       <c r="G557" s="2" t="n">
-        <v>0.91</v>
+        <v>0.4083</v>
       </c>
       <c r="H557" s="3" t="n"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-537</t>
+          <t>PL-RT-581</t>
         </is>
       </c>
       <c r="B558" s="2" t="inlineStr">
         <is>
-          <t>電纜線架</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C558" s="2" t="inlineStr">
         <is>
-          <t>2MM(厚度) 伸縮直式電纜線架 1000W</t>
+          <t>2MM預鑄式 6.6KV以下 30m/m2-38m/m2</t>
         </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E558" s="2" t="inlineStr">
@@ -20552,29 +20551,29 @@
         </is>
       </c>
       <c r="G558" s="2" t="n">
-        <v>0.287</v>
+        <v>0.282</v>
       </c>
       <c r="H558" s="3" t="n"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-529</t>
+          <t>PL-RT-587</t>
         </is>
       </c>
       <c r="B559" s="2" t="inlineStr">
         <is>
-          <t>電纜線架</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C559" s="2" t="inlineStr">
         <is>
-          <t>2MM(厚度) 伸縮直式電纜線架 200W</t>
+          <t>2MM預鑄式 6.6KV以下 325m/m2</t>
         </is>
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E559" s="2" t="inlineStr">
@@ -20588,29 +20587,29 @@
         </is>
       </c>
       <c r="G559" s="2" t="n">
-        <v>0.125</v>
+        <v>0.44</v>
       </c>
       <c r="H559" s="3" t="n"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-530</t>
+          <t>PL-RT-582</t>
         </is>
       </c>
       <c r="B560" s="2" t="inlineStr">
         <is>
-          <t>電纜線架</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>2MM(厚度) 伸縮直式電纜線架 300W</t>
+          <t>2MM預鑄式 6.6KV以下 50m/m2-60m/m2</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
@@ -20624,29 +20623,29 @@
         </is>
       </c>
       <c r="G560" s="2" t="n">
-        <v>0.145</v>
+        <v>0.298</v>
       </c>
       <c r="H560" s="3" t="n"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
         <is>
-          <t>PL-RT-531</t>
+          <t>PL-RT-583</t>
         </is>
       </c>
       <c r="B561" s="2" t="inlineStr">
         <is>
-          <t>電纜線架</t>
+          <t>電纜頭處理</t>
         </is>
       </c>
       <c r="C561" s="2" t="inlineStr">
         <is>
-          <t>2MM(厚度) 伸縮直式電纜線架 400W</t>
+          <t>2MM預鑄式 6.6KV以下 80m/m2-100m/m2</t>
         </is>
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>只</t>
         </is>
       </c>
       <c r="E561" s="2" t="inlineStr">
@@ -20660,1380 +20659,12 @@
         </is>
       </c>
       <c r="G561" s="2" t="n">
-        <v>0.165</v>
+        <v>0.329</v>
       </c>
       <c r="H561" s="3" t="n"/>
     </row>
-    <row r="562">
-      <c r="A562" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-532</t>
-        </is>
-      </c>
-      <c r="B562" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C562" s="2" t="inlineStr">
-        <is>
-          <t>2MM(厚度) 伸縮直式電纜線架 500W</t>
-        </is>
-      </c>
-      <c r="D562" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E562" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F562" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G562" s="2" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="H562" s="3" t="n"/>
-    </row>
-    <row r="563">
-      <c r="A563" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-533</t>
-        </is>
-      </c>
-      <c r="B563" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C563" s="2" t="inlineStr">
-        <is>
-          <t>2MM(厚度) 伸縮直式電纜線架 600W</t>
-        </is>
-      </c>
-      <c r="D563" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E563" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F563" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G563" s="2" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="H563" s="3" t="n"/>
-    </row>
-    <row r="564">
-      <c r="A564" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-534</t>
-        </is>
-      </c>
-      <c r="B564" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C564" s="2" t="inlineStr">
-        <is>
-          <t>2MM(厚度) 伸縮直式電纜線架 700W</t>
-        </is>
-      </c>
-      <c r="D564" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E564" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F564" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G564" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="H564" s="3" t="n"/>
-    </row>
-    <row r="565">
-      <c r="A565" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-535</t>
-        </is>
-      </c>
-      <c r="B565" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C565" s="2" t="inlineStr">
-        <is>
-          <t>2MM(厚度) 伸縮直式電纜線架 800W</t>
-        </is>
-      </c>
-      <c r="D565" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E565" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F565" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G565" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="H565" s="3" t="n"/>
-    </row>
-    <row r="566">
-      <c r="A566" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-536</t>
-        </is>
-      </c>
-      <c r="B566" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C566" s="2" t="inlineStr">
-        <is>
-          <t>2MM(厚度) 伸縮直式電纜線架 900W</t>
-        </is>
-      </c>
-      <c r="D566" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E566" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F566" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G566" s="2" t="n">
-        <v>0.249</v>
-      </c>
-      <c r="H566" s="3" t="n"/>
-    </row>
-    <row r="567">
-      <c r="A567" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-546</t>
-        </is>
-      </c>
-      <c r="B567" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C567" s="2" t="inlineStr">
-        <is>
-          <t>3MM(厚度) 伸縮直式電纜線架 1000W</t>
-        </is>
-      </c>
-      <c r="D567" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E567" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F567" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G567" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="H567" s="3" t="n"/>
-    </row>
-    <row r="568">
-      <c r="A568" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-538</t>
-        </is>
-      </c>
-      <c r="B568" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C568" s="2" t="inlineStr">
-        <is>
-          <t>3MM(厚度) 伸縮直式電纜線架 200W</t>
-        </is>
-      </c>
-      <c r="D568" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E568" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F568" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G568" s="2" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="H568" s="3" t="n"/>
-    </row>
-    <row r="569">
-      <c r="A569" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-539</t>
-        </is>
-      </c>
-      <c r="B569" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C569" s="2" t="inlineStr">
-        <is>
-          <t>3MM(厚度) 伸縮直式電纜線架 300W</t>
-        </is>
-      </c>
-      <c r="D569" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E569" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F569" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G569" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="H569" s="3" t="n"/>
-    </row>
-    <row r="570">
-      <c r="A570" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-540</t>
-        </is>
-      </c>
-      <c r="B570" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C570" s="2" t="inlineStr">
-        <is>
-          <t>3MM(厚度) 伸縮直式電纜線架 400W</t>
-        </is>
-      </c>
-      <c r="D570" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E570" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F570" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G570" s="2" t="n">
-        <v>0.173</v>
-      </c>
-      <c r="H570" s="3" t="n"/>
-    </row>
-    <row r="571">
-      <c r="A571" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-541</t>
-        </is>
-      </c>
-      <c r="B571" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C571" s="2" t="inlineStr">
-        <is>
-          <t>3MM(厚度) 伸縮直式電纜線架 500W</t>
-        </is>
-      </c>
-      <c r="D571" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E571" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F571" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G571" s="2" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="H571" s="3" t="n"/>
-    </row>
-    <row r="572">
-      <c r="A572" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-542</t>
-        </is>
-      </c>
-      <c r="B572" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C572" s="2" t="inlineStr">
-        <is>
-          <t>3MM(厚度) 伸縮直式電纜線架 600W</t>
-        </is>
-      </c>
-      <c r="D572" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E572" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F572" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G572" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="H572" s="3" t="n"/>
-    </row>
-    <row r="573">
-      <c r="A573" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-543</t>
-        </is>
-      </c>
-      <c r="B573" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C573" s="2" t="inlineStr">
-        <is>
-          <t>3MM(厚度) 伸縮直式電纜線架 700W</t>
-        </is>
-      </c>
-      <c r="D573" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E573" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F573" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G573" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="H573" s="3" t="n"/>
-    </row>
-    <row r="574">
-      <c r="A574" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-544</t>
-        </is>
-      </c>
-      <c r="B574" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C574" s="2" t="inlineStr">
-        <is>
-          <t>3MM(厚度) 伸縮直式電纜線架 800W</t>
-        </is>
-      </c>
-      <c r="D574" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E574" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F574" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G574" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="H574" s="3" t="n"/>
-    </row>
-    <row r="575">
-      <c r="A575" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-545</t>
-        </is>
-      </c>
-      <c r="B575" s="2" t="inlineStr">
-        <is>
-          <t>電纜線架</t>
-        </is>
-      </c>
-      <c r="C575" s="2" t="inlineStr">
-        <is>
-          <t>3MM(厚度) 伸縮直式電纜線架 900W</t>
-        </is>
-      </c>
-      <c r="D575" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="E575" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F575" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G575" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="H575" s="3" t="n"/>
-    </row>
-    <row r="576">
-      <c r="A576" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-592</t>
-        </is>
-      </c>
-      <c r="B576" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C576" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 15KV 125m/m2-150m/m2</t>
-        </is>
-      </c>
-      <c r="D576" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E576" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F576" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G576" s="2" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="H576" s="3" t="n"/>
-    </row>
-    <row r="577">
-      <c r="A577" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-593</t>
-        </is>
-      </c>
-      <c r="B577" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C577" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 15KV 200m/m2</t>
-        </is>
-      </c>
-      <c r="D577" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E577" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F577" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G577" s="2" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="H577" s="3" t="n"/>
-    </row>
-    <row r="578">
-      <c r="A578" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-588</t>
-        </is>
-      </c>
-      <c r="B578" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C578" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 15KV 22m/m2以下</t>
-        </is>
-      </c>
-      <c r="D578" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E578" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F578" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G578" s="2" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="H578" s="3" t="n"/>
-    </row>
-    <row r="579">
-      <c r="A579" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-594</t>
-        </is>
-      </c>
-      <c r="B579" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C579" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 15KV 250m/m2</t>
-        </is>
-      </c>
-      <c r="D579" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E579" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F579" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G579" s="2" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="H579" s="3" t="n"/>
-    </row>
-    <row r="580">
-      <c r="A580" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-589</t>
-        </is>
-      </c>
-      <c r="B580" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C580" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 15KV 30m/m2-38m/m2</t>
-        </is>
-      </c>
-      <c r="D580" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E580" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F580" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G580" s="2" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="H580" s="3" t="n"/>
-    </row>
-    <row r="581">
-      <c r="A581" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-595</t>
-        </is>
-      </c>
-      <c r="B581" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C581" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 15KV 325m/m2</t>
-        </is>
-      </c>
-      <c r="D581" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E581" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F581" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G581" s="2" t="n">
-        <v>0.628</v>
-      </c>
-      <c r="H581" s="3" t="n"/>
-    </row>
-    <row r="582">
-      <c r="A582" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-590</t>
-        </is>
-      </c>
-      <c r="B582" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C582" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 15KV 50m/m2-60m/m2</t>
-        </is>
-      </c>
-      <c r="D582" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E582" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F582" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G582" s="2" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="H582" s="3" t="n"/>
-    </row>
-    <row r="583">
-      <c r="A583" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-591</t>
-        </is>
-      </c>
-      <c r="B583" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C583" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 15KV 80m/m2-100m/m2</t>
-        </is>
-      </c>
-      <c r="D583" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E583" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F583" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G583" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H583" s="3" t="n"/>
-    </row>
-    <row r="584">
-      <c r="A584" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-600</t>
-        </is>
-      </c>
-      <c r="B584" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C584" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 25KV 125m/m2-150m/m2</t>
-        </is>
-      </c>
-      <c r="D584" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E584" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F584" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G584" s="2" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="H584" s="3" t="n"/>
-    </row>
-    <row r="585">
-      <c r="A585" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-601</t>
-        </is>
-      </c>
-      <c r="B585" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C585" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 25KV 200m/m2</t>
-        </is>
-      </c>
-      <c r="D585" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E585" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F585" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G585" s="2" t="n">
-        <v>0.628</v>
-      </c>
-      <c r="H585" s="3" t="n"/>
-    </row>
-    <row r="586">
-      <c r="A586" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-596</t>
-        </is>
-      </c>
-      <c r="B586" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C586" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 25KV 22m/m2以下</t>
-        </is>
-      </c>
-      <c r="D586" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E586" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F586" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G586" s="2" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="H586" s="3" t="n"/>
-    </row>
-    <row r="587">
-      <c r="A587" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-602</t>
-        </is>
-      </c>
-      <c r="B587" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C587" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 25KV 250m/m2</t>
-        </is>
-      </c>
-      <c r="D587" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E587" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F587" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G587" s="2" t="n">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="H587" s="3" t="n"/>
-    </row>
-    <row r="588">
-      <c r="A588" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-597</t>
-        </is>
-      </c>
-      <c r="B588" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C588" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 25KV 30m/m2-38m/m2</t>
-        </is>
-      </c>
-      <c r="D588" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E588" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F588" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G588" s="2" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="H588" s="3" t="n"/>
-    </row>
-    <row r="589">
-      <c r="A589" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-603</t>
-        </is>
-      </c>
-      <c r="B589" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C589" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 25KV 325m/m2</t>
-        </is>
-      </c>
-      <c r="D589" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E589" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F589" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G589" s="2" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="H589" s="3" t="n"/>
-    </row>
-    <row r="590">
-      <c r="A590" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-598</t>
-        </is>
-      </c>
-      <c r="B590" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C590" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 25KV 50m/m2-60m/m2</t>
-        </is>
-      </c>
-      <c r="D590" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E590" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F590" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G590" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H590" s="3" t="n"/>
-    </row>
-    <row r="591">
-      <c r="A591" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-599</t>
-        </is>
-      </c>
-      <c r="B591" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C591" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 25KV 80m/m2-100m/m2</t>
-        </is>
-      </c>
-      <c r="D591" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E591" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F591" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G591" s="2" t="n">
-        <v>0.502</v>
-      </c>
-      <c r="H591" s="3" t="n"/>
-    </row>
-    <row r="592">
-      <c r="A592" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-584</t>
-        </is>
-      </c>
-      <c r="B592" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C592" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 6.6KV以下 125m/m2-150m/m2</t>
-        </is>
-      </c>
-      <c r="D592" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E592" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F592" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G592" s="2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="H592" s="3" t="n"/>
-    </row>
-    <row r="593">
-      <c r="A593" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-585</t>
-        </is>
-      </c>
-      <c r="B593" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C593" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 6.6KV以下 200m/m2</t>
-        </is>
-      </c>
-      <c r="D593" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E593" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F593" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G593" s="2" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="H593" s="3" t="n"/>
-    </row>
-    <row r="594">
-      <c r="A594" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-580</t>
-        </is>
-      </c>
-      <c r="B594" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C594" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 6.6KV以下 22m/m2以下</t>
-        </is>
-      </c>
-      <c r="D594" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E594" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F594" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G594" s="2" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="H594" s="3" t="n"/>
-    </row>
-    <row r="595">
-      <c r="A595" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-586</t>
-        </is>
-      </c>
-      <c r="B595" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C595" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 6.6KV以下 250m/m2</t>
-        </is>
-      </c>
-      <c r="D595" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E595" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F595" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G595" s="2" t="n">
-        <v>0.4083</v>
-      </c>
-      <c r="H595" s="3" t="n"/>
-    </row>
-    <row r="596">
-      <c r="A596" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-581</t>
-        </is>
-      </c>
-      <c r="B596" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C596" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 6.6KV以下 30m/m2-38m/m2</t>
-        </is>
-      </c>
-      <c r="D596" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E596" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F596" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G596" s="2" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="H596" s="3" t="n"/>
-    </row>
-    <row r="597">
-      <c r="A597" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-587</t>
-        </is>
-      </c>
-      <c r="B597" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C597" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 6.6KV以下 325m/m2</t>
-        </is>
-      </c>
-      <c r="D597" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E597" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F597" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G597" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H597" s="3" t="n"/>
-    </row>
-    <row r="598">
-      <c r="A598" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-582</t>
-        </is>
-      </c>
-      <c r="B598" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C598" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 6.6KV以下 50m/m2-60m/m2</t>
-        </is>
-      </c>
-      <c r="D598" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E598" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F598" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G598" s="2" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="H598" s="3" t="n"/>
-    </row>
-    <row r="599">
-      <c r="A599" s="2" t="inlineStr">
-        <is>
-          <t>PL-RT-583</t>
-        </is>
-      </c>
-      <c r="B599" s="2" t="inlineStr">
-        <is>
-          <t>電纜頭處理</t>
-        </is>
-      </c>
-      <c r="C599" s="2" t="inlineStr">
-        <is>
-          <t>2MM預鑄式 6.6KV以下 80m/m2-100m/m2</t>
-        </is>
-      </c>
-      <c r="D599" s="2" t="inlineStr">
-        <is>
-          <t>只</t>
-        </is>
-      </c>
-      <c r="E599" s="2" t="inlineStr">
-        <is>
-          <t>電線</t>
-        </is>
-      </c>
-      <c r="F599" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G599" s="2" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="H599" s="3" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H599"/>
+  <autoFilter ref="A1:H561"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>